--- a/research/traditional_assets/database/data/pakistan/pakistan_cable_tv.xlsx
+++ b/research/traditional_assets/database/data/pakistan/pakistan_cable_tv.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1425931732704709</v>
+        <v>0.1422116030679866</v>
       </c>
       <c r="C2">
-        <v>60.50304921089505</v>
+        <v>60.03823532052121</v>
       </c>
       <c r="D2">
-        <v>52.10304921089505</v>
+        <v>52.24208532052121</v>
       </c>
       <c r="E2">
-        <v>-0.6850000000000001</v>
+        <v>-0.08114999999999994</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.6038500000000001</v>
       </c>
       <c r="G2">
         <v>8.4</v>
@@ -1445,28 +1445,28 @@
         <v>11.6</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.030373655</v>
       </c>
       <c r="N2">
-        <v>11.6</v>
+        <v>11.569626345</v>
       </c>
       <c r="O2">
-        <v>3.364</v>
+        <v>3.35519164005</v>
       </c>
       <c r="P2">
-        <v>8.236000000000001</v>
+        <v>8.214434704949999</v>
       </c>
       <c r="Q2">
-        <v>8.836</v>
+        <v>8.814434704949999</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1425931732704709</v>
+        <v>0.1432873465333198</v>
       </c>
       <c r="T2">
-        <v>0.5919749984509941</v>
+        <v>0.5962204757126124</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>381.9099150233977</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1422116030679866</v>
+        <v>0.1418300328655022</v>
       </c>
       <c r="C3">
-        <v>60.03823532052121</v>
+        <v>59.57416544657824</v>
       </c>
       <c r="D3">
-        <v>52.24208532052121</v>
+        <v>52.38186544657825</v>
       </c>
       <c r="E3">
-        <v>-0.08114999999999994</v>
+        <v>0.5227000000000002</v>
       </c>
       <c r="F3">
-        <v>0.6038500000000001</v>
+        <v>1.2077</v>
       </c>
       <c r="G3">
         <v>8.4</v>
@@ -1527,28 +1527,28 @@
         <v>11.6</v>
       </c>
       <c r="M3">
-        <v>0.030373655</v>
+        <v>0.06074731000000001</v>
       </c>
       <c r="N3">
-        <v>11.569626345</v>
+        <v>11.53925269</v>
       </c>
       <c r="O3">
-        <v>3.35519164005</v>
+        <v>3.3463832801</v>
       </c>
       <c r="P3">
-        <v>8.214434704949999</v>
+        <v>8.1928694099</v>
       </c>
       <c r="Q3">
-        <v>8.814434704949999</v>
+        <v>8.7928694099</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1432873465333198</v>
+        <v>0.1439956865974512</v>
       </c>
       <c r="T3">
-        <v>0.5962204757126124</v>
+        <v>0.6005525953673249</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>381.9099150233977</v>
+        <v>190.9549575116988</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1418300328655022</v>
+        <v>0.1414484626630179</v>
       </c>
       <c r="C4">
-        <v>59.57416544657824</v>
+        <v>59.11084557721058</v>
       </c>
       <c r="D4">
-        <v>52.38186544657825</v>
+        <v>52.52239557721058</v>
       </c>
       <c r="E4">
-        <v>0.5227000000000002</v>
+        <v>1.12655</v>
       </c>
       <c r="F4">
-        <v>1.2077</v>
+        <v>1.81155</v>
       </c>
       <c r="G4">
         <v>8.4</v>
@@ -1609,28 +1609,28 @@
         <v>11.6</v>
       </c>
       <c r="M4">
-        <v>0.06074731000000001</v>
+        <v>0.091120965</v>
       </c>
       <c r="N4">
-        <v>11.53925269</v>
+        <v>11.508879035</v>
       </c>
       <c r="O4">
-        <v>3.3463832801</v>
+        <v>3.33757492015</v>
       </c>
       <c r="P4">
-        <v>8.1928694099</v>
+        <v>8.171304114849999</v>
       </c>
       <c r="Q4">
-        <v>8.7928694099</v>
+        <v>8.771304114849999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1439956865974512</v>
+        <v>0.1447186316113586</v>
       </c>
       <c r="T4">
-        <v>0.6005525953673249</v>
+        <v>0.6049740370767738</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>190.9549575116988</v>
+        <v>127.3033050077993</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1414484626630179</v>
+        <v>0.1410668924605335</v>
       </c>
       <c r="C5">
-        <v>59.11084557721058</v>
+        <v>58.64828176499561</v>
       </c>
       <c r="D5">
-        <v>52.52239557721058</v>
+        <v>52.66368176499561</v>
       </c>
       <c r="E5">
-        <v>1.12655</v>
+        <v>1.7304</v>
       </c>
       <c r="F5">
-        <v>1.81155</v>
+        <v>2.4154</v>
       </c>
       <c r="G5">
         <v>8.4</v>
@@ -1691,28 +1691,28 @@
         <v>11.6</v>
       </c>
       <c r="M5">
-        <v>0.091120965</v>
+        <v>0.12149462</v>
       </c>
       <c r="N5">
-        <v>11.508879035</v>
+        <v>11.47850538</v>
       </c>
       <c r="O5">
-        <v>3.33757492015</v>
+        <v>3.3287665602</v>
       </c>
       <c r="P5">
-        <v>8.171304114849999</v>
+        <v>8.1497388198</v>
       </c>
       <c r="Q5">
-        <v>8.771304114849999</v>
+        <v>8.749738819799999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1447186316113586</v>
+        <v>0.1454566379797224</v>
       </c>
       <c r="T5">
-        <v>0.6049740370767738</v>
+        <v>0.6094875921551693</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>127.3033050077993</v>
+        <v>95.47747875584942</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1410668924605335</v>
+        <v>0.1406853222580491</v>
       </c>
       <c r="C6">
-        <v>58.64828176499561</v>
+        <v>58.18648012781249</v>
       </c>
       <c r="D6">
-        <v>52.66368176499561</v>
+        <v>52.80573012781249</v>
       </c>
       <c r="E6">
-        <v>1.7304</v>
+        <v>2.33425</v>
       </c>
       <c r="F6">
-        <v>2.4154</v>
+        <v>3.01925</v>
       </c>
       <c r="G6">
         <v>8.4</v>
@@ -1773,28 +1773,28 @@
         <v>11.6</v>
       </c>
       <c r="M6">
-        <v>0.12149462</v>
+        <v>0.151868275</v>
       </c>
       <c r="N6">
-        <v>11.47850538</v>
+        <v>11.448131725</v>
       </c>
       <c r="O6">
-        <v>3.3287665602</v>
+        <v>3.31995820025</v>
       </c>
       <c r="P6">
-        <v>8.1497388198</v>
+        <v>8.12817352475</v>
       </c>
       <c r="Q6">
-        <v>8.749738819799999</v>
+        <v>8.72817352475</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1454566379797224</v>
+        <v>0.1462101813242622</v>
       </c>
       <c r="T6">
-        <v>0.6094875921551693</v>
+        <v>0.6140961694457417</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>95.47747875584942</v>
+        <v>76.38198300467954</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1406853222580491</v>
+        <v>0.1403037520555648</v>
       </c>
       <c r="C7">
-        <v>58.18648012781249</v>
+        <v>57.7254468497253</v>
       </c>
       <c r="D7">
-        <v>52.80573012781249</v>
+        <v>52.9485468497253</v>
       </c>
       <c r="E7">
-        <v>2.33425</v>
+        <v>2.9381</v>
       </c>
       <c r="F7">
-        <v>3.01925</v>
+        <v>3.6231</v>
       </c>
       <c r="G7">
         <v>8.4</v>
@@ -1855,28 +1855,28 @@
         <v>11.6</v>
       </c>
       <c r="M7">
-        <v>0.151868275</v>
+        <v>0.18224193</v>
       </c>
       <c r="N7">
-        <v>11.448131725</v>
+        <v>11.41775807</v>
       </c>
       <c r="O7">
-        <v>3.31995820025</v>
+        <v>3.3111498403</v>
       </c>
       <c r="P7">
-        <v>8.12817352475</v>
+        <v>8.106608229700001</v>
       </c>
       <c r="Q7">
-        <v>8.72817352475</v>
+        <v>8.7066082297</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1462101813242622</v>
+        <v>0.1469797575059199</v>
       </c>
       <c r="T7">
-        <v>0.6140961694457417</v>
+        <v>0.6188028015722838</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>76.38198300467954</v>
+        <v>63.65165250389961</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1403037520555648</v>
+        <v>0.1399221818530804</v>
       </c>
       <c r="C8">
-        <v>57.7254468497253</v>
+        <v>57.26518818188045</v>
       </c>
       <c r="D8">
-        <v>52.9485468497253</v>
+        <v>53.09213818188046</v>
       </c>
       <c r="E8">
-        <v>2.9381</v>
+        <v>3.541949999999999</v>
       </c>
       <c r="F8">
-        <v>3.6231</v>
+        <v>4.22695</v>
       </c>
       <c r="G8">
         <v>8.4</v>
@@ -1937,28 +1937,28 @@
         <v>11.6</v>
       </c>
       <c r="M8">
-        <v>0.18224193</v>
+        <v>0.212615585</v>
       </c>
       <c r="N8">
-        <v>11.41775807</v>
+        <v>11.387384415</v>
       </c>
       <c r="O8">
-        <v>3.3111498403</v>
+        <v>3.30234148035</v>
       </c>
       <c r="P8">
-        <v>8.106608229700001</v>
+        <v>8.08504293465</v>
       </c>
       <c r="Q8">
-        <v>8.7066082297</v>
+        <v>8.685042934649999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1469797575059199</v>
+        <v>0.1477658837129897</v>
       </c>
       <c r="T8">
-        <v>0.6188028015722838</v>
+        <v>0.6236106515940204</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>63.65165250389963</v>
+        <v>54.55855928905682</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1399221818530804</v>
+        <v>0.139540611650596</v>
       </c>
       <c r="C9">
-        <v>57.26518818188046</v>
+        <v>56.80571044341877</v>
       </c>
       <c r="D9">
-        <v>53.09213818188046</v>
+        <v>53.23651044341878</v>
       </c>
       <c r="E9">
-        <v>3.54195</v>
+        <v>4.145800000000001</v>
       </c>
       <c r="F9">
-        <v>4.22695</v>
+        <v>4.830800000000001</v>
       </c>
       <c r="G9">
         <v>8.4</v>
@@ -2019,28 +2019,28 @@
         <v>11.6</v>
       </c>
       <c r="M9">
-        <v>0.212615585</v>
+        <v>0.24298924</v>
       </c>
       <c r="N9">
-        <v>11.387384415</v>
+        <v>11.35701076</v>
       </c>
       <c r="O9">
-        <v>3.30234148035</v>
+        <v>3.2935331204</v>
       </c>
       <c r="P9">
-        <v>8.08504293465</v>
+        <v>8.0634776396</v>
       </c>
       <c r="Q9">
-        <v>8.685042934649999</v>
+        <v>8.6634776396</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1477658837129897</v>
+        <v>0.1485690996202131</v>
       </c>
       <c r="T9">
-        <v>0.6236106515940204</v>
+        <v>0.6285230200944902</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>54.55855928905682</v>
+        <v>47.73873937792471</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.139540611650596</v>
+        <v>0.1391590414481116</v>
       </c>
       <c r="C10">
-        <v>56.80571044341877</v>
+        <v>56.34702002240249</v>
       </c>
       <c r="D10">
-        <v>53.23651044341878</v>
+        <v>53.38167002240249</v>
       </c>
       <c r="E10">
-        <v>4.145800000000001</v>
+        <v>4.749650000000001</v>
       </c>
       <c r="F10">
-        <v>4.830800000000001</v>
+        <v>5.43465</v>
       </c>
       <c r="G10">
         <v>8.4</v>
@@ -2101,28 +2101,28 @@
         <v>11.6</v>
       </c>
       <c r="M10">
-        <v>0.24298924</v>
+        <v>0.273362895</v>
       </c>
       <c r="N10">
-        <v>11.35701076</v>
+        <v>11.326637105</v>
       </c>
       <c r="O10">
-        <v>3.2935331204</v>
+        <v>3.28472476045</v>
       </c>
       <c r="P10">
-        <v>8.0634776396</v>
+        <v>8.041912344549999</v>
       </c>
       <c r="Q10">
-        <v>8.6634776396</v>
+        <v>8.641912344549999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1485690996202131</v>
+        <v>0.1493899686242985</v>
       </c>
       <c r="T10">
-        <v>0.6285230200944902</v>
+        <v>0.6335433527378276</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>47.73873937792471</v>
+        <v>42.43443500259975</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1391590414481116</v>
+        <v>0.1387774712456273</v>
       </c>
       <c r="C11">
-        <v>56.34702002240249</v>
+        <v>55.88912337675743</v>
       </c>
       <c r="D11">
-        <v>53.38167002240249</v>
+        <v>53.52762337675743</v>
       </c>
       <c r="E11">
-        <v>4.749650000000001</v>
+        <v>5.3535</v>
       </c>
       <c r="F11">
-        <v>5.43465</v>
+        <v>6.0385</v>
       </c>
       <c r="G11">
         <v>8.4</v>
@@ -2183,28 +2183,28 @@
         <v>11.6</v>
       </c>
       <c r="M11">
-        <v>0.273362895</v>
+        <v>0.30373655</v>
       </c>
       <c r="N11">
-        <v>11.326637105</v>
+        <v>11.29626345</v>
       </c>
       <c r="O11">
-        <v>3.28472476045</v>
+        <v>3.2759164005</v>
       </c>
       <c r="P11">
-        <v>8.041912344549999</v>
+        <v>8.0203470495</v>
       </c>
       <c r="Q11">
-        <v>8.641912344549999</v>
+        <v>8.620347049499999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1493899686242985</v>
+        <v>0.1502290791618081</v>
       </c>
       <c r="T11">
-        <v>0.6335433527378276</v>
+        <v>0.6386752483287947</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>42.43443500259975</v>
+        <v>38.19099150233978</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1387774712456273</v>
+        <v>0.1383959010431429</v>
       </c>
       <c r="C12">
-        <v>55.88912337675743</v>
+        <v>55.43202703523075</v>
       </c>
       <c r="D12">
-        <v>53.52762337675743</v>
+        <v>53.67437703523075</v>
       </c>
       <c r="E12">
-        <v>5.3535</v>
+        <v>5.95735</v>
       </c>
       <c r="F12">
-        <v>6.038500000000001</v>
+        <v>6.64235</v>
       </c>
       <c r="G12">
         <v>8.4</v>
@@ -2265,28 +2265,28 @@
         <v>11.6</v>
       </c>
       <c r="M12">
-        <v>0.30373655</v>
+        <v>0.334110205</v>
       </c>
       <c r="N12">
-        <v>11.29626345</v>
+        <v>11.265889795</v>
       </c>
       <c r="O12">
-        <v>3.2759164005</v>
+        <v>3.26710804055</v>
       </c>
       <c r="P12">
-        <v>8.0203470495</v>
+        <v>7.99878175445</v>
       </c>
       <c r="Q12">
-        <v>8.620347049499999</v>
+        <v>8.59878175445</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1502290791618081</v>
+        <v>0.1510870461158909</v>
       </c>
       <c r="T12">
-        <v>0.6386752483287947</v>
+        <v>0.6439224674161881</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>38.19099150233977</v>
+        <v>34.71908318394525</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1383959010431429</v>
+        <v>0.1380143308406586</v>
       </c>
       <c r="C13">
-        <v>55.43202703523075</v>
+        <v>54.97573759836445</v>
       </c>
       <c r="D13">
-        <v>53.67437703523075</v>
+        <v>53.82193759836445</v>
       </c>
       <c r="E13">
-        <v>5.95735</v>
+        <v>6.561199999999999</v>
       </c>
       <c r="F13">
-        <v>6.64235</v>
+        <v>7.2462</v>
       </c>
       <c r="G13">
         <v>8.4</v>
@@ -2347,28 +2347,28 @@
         <v>11.6</v>
       </c>
       <c r="M13">
-        <v>0.334110205</v>
+        <v>0.36448386</v>
       </c>
       <c r="N13">
-        <v>11.265889795</v>
+        <v>11.23551614</v>
       </c>
       <c r="O13">
-        <v>3.26710804055</v>
+        <v>3.2582996806</v>
       </c>
       <c r="P13">
-        <v>7.99878175445</v>
+        <v>7.9772164594</v>
       </c>
       <c r="Q13">
-        <v>8.59878175445</v>
+        <v>8.577216459399999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1510870461158909</v>
+        <v>0.1519645123189302</v>
       </c>
       <c r="T13">
-        <v>0.6439224674161881</v>
+        <v>0.6492889414828403</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>34.71908318394525</v>
+        <v>31.82582625194981</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1380143308406586</v>
+        <v>0.1376327606381742</v>
       </c>
       <c r="C14">
-        <v>54.97573759836445</v>
+        <v>54.52026173948494</v>
       </c>
       <c r="D14">
-        <v>53.82193759836445</v>
+        <v>53.97031173948495</v>
       </c>
       <c r="E14">
-        <v>6.561199999999999</v>
+        <v>7.165050000000001</v>
       </c>
       <c r="F14">
-        <v>7.2462</v>
+        <v>7.850050000000001</v>
       </c>
       <c r="G14">
         <v>8.4</v>
@@ -2429,28 +2429,28 @@
         <v>11.6</v>
       </c>
       <c r="M14">
-        <v>0.36448386</v>
+        <v>0.394857515</v>
       </c>
       <c r="N14">
-        <v>11.23551614</v>
+        <v>11.205142485</v>
       </c>
       <c r="O14">
-        <v>3.2582996806</v>
+        <v>3.24949132065</v>
       </c>
       <c r="P14">
-        <v>7.9772164594</v>
+        <v>7.95565116435</v>
       </c>
       <c r="Q14">
-        <v>8.577216459399999</v>
+        <v>8.55565116435</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1519645123189302</v>
+        <v>0.1528621501588209</v>
       </c>
       <c r="T14">
-        <v>0.6492889414828403</v>
+        <v>0.6547787827694157</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>31.82582625194981</v>
+        <v>29.37768577103059</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1376327606381742</v>
+        <v>0.1372511904356898</v>
       </c>
       <c r="C15">
-        <v>54.52026173948494</v>
+        <v>54.0656062057091</v>
       </c>
       <c r="D15">
-        <v>53.97031173948495</v>
+        <v>54.1195062057091</v>
       </c>
       <c r="E15">
-        <v>7.165050000000001</v>
+        <v>7.7689</v>
       </c>
       <c r="F15">
-        <v>7.850050000000001</v>
+        <v>8.453900000000001</v>
       </c>
       <c r="G15">
         <v>8.4</v>
@@ -2511,28 +2511,28 @@
         <v>11.6</v>
       </c>
       <c r="M15">
-        <v>0.394857515</v>
+        <v>0.42523117</v>
       </c>
       <c r="N15">
-        <v>11.205142485</v>
+        <v>11.17476883</v>
       </c>
       <c r="O15">
-        <v>3.24949132065</v>
+        <v>3.2406829607</v>
       </c>
       <c r="P15">
-        <v>7.95565116435</v>
+        <v>7.9340858693</v>
       </c>
       <c r="Q15">
-        <v>8.55565116435</v>
+        <v>8.5340858693</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1528621501588209</v>
+        <v>0.1537806632973137</v>
       </c>
       <c r="T15">
-        <v>0.6547787827694157</v>
+        <v>0.6603962947835857</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>29.37768577103059</v>
+        <v>27.27927964452841</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1372511904356898</v>
+        <v>0.1368696202332055</v>
       </c>
       <c r="C16">
-        <v>54.0656062057091</v>
+        <v>53.61177781896697</v>
       </c>
       <c r="D16">
-        <v>54.1195062057091</v>
+        <v>54.26952781896697</v>
       </c>
       <c r="E16">
-        <v>7.7689</v>
+        <v>8.372750000000002</v>
       </c>
       <c r="F16">
-        <v>8.453900000000001</v>
+        <v>9.057750000000002</v>
       </c>
       <c r="G16">
         <v>8.4</v>
@@ -2593,28 +2593,28 @@
         <v>11.6</v>
       </c>
       <c r="M16">
-        <v>0.42523117</v>
+        <v>0.4556048250000001</v>
       </c>
       <c r="N16">
-        <v>11.17476883</v>
+        <v>11.144395175</v>
       </c>
       <c r="O16">
-        <v>3.2406829607</v>
+        <v>3.23187460075</v>
       </c>
       <c r="P16">
-        <v>7.9340858693</v>
+        <v>7.912520574249999</v>
       </c>
       <c r="Q16">
-        <v>8.5340858693</v>
+        <v>8.512520574249999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1537806632973137</v>
+        <v>0.1547207885096535</v>
       </c>
       <c r="T16">
-        <v>0.6603962947835857</v>
+        <v>0.6661459835510304</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>27.27927964452841</v>
+        <v>25.46066100155984</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1368696202332055</v>
+        <v>0.1364880500307211</v>
       </c>
       <c r="C17">
-        <v>53.61177781896697</v>
+        <v>53.15878347704161</v>
       </c>
       <c r="D17">
-        <v>54.26952781896697</v>
+        <v>54.42038347704161</v>
       </c>
       <c r="E17">
-        <v>8.37275</v>
+        <v>8.976600000000001</v>
       </c>
       <c r="F17">
-        <v>9.05775</v>
+        <v>9.661600000000002</v>
       </c>
       <c r="G17">
         <v>8.4</v>
@@ -2675,28 +2675,28 @@
         <v>11.6</v>
       </c>
       <c r="M17">
-        <v>0.455604825</v>
+        <v>0.48597848</v>
       </c>
       <c r="N17">
-        <v>11.144395175</v>
+        <v>11.11402152</v>
       </c>
       <c r="O17">
-        <v>3.23187460075</v>
+        <v>3.2230662408</v>
       </c>
       <c r="P17">
-        <v>7.912520574249999</v>
+        <v>7.8909552792</v>
       </c>
       <c r="Q17">
-        <v>8.512520574249999</v>
+        <v>8.4909552792</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1547207885096535</v>
+        <v>0.1556832976556203</v>
       </c>
       <c r="T17">
-        <v>0.6661459835510304</v>
+        <v>0.6720325696700808</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>25.46066100155985</v>
+        <v>23.86936968896235</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1364880500307211</v>
+        <v>0.1361064798282367</v>
       </c>
       <c r="C18">
-        <v>53.15878347704161</v>
+        <v>52.70663015462634</v>
       </c>
       <c r="D18">
-        <v>54.42038347704161</v>
+        <v>54.57208015462634</v>
       </c>
       <c r="E18">
-        <v>8.976600000000001</v>
+        <v>9.580450000000001</v>
       </c>
       <c r="F18">
-        <v>9.661600000000002</v>
+        <v>10.26545</v>
       </c>
       <c r="G18">
         <v>8.4</v>
@@ -2757,28 +2757,28 @@
         <v>11.6</v>
       </c>
       <c r="M18">
-        <v>0.48597848</v>
+        <v>0.516352135</v>
       </c>
       <c r="N18">
-        <v>11.11402152</v>
+        <v>11.083647865</v>
       </c>
       <c r="O18">
-        <v>3.2230662408</v>
+        <v>3.21425788085</v>
       </c>
       <c r="P18">
-        <v>7.8909552792</v>
+        <v>7.869389984150001</v>
       </c>
       <c r="Q18">
-        <v>8.4909552792</v>
+        <v>8.46938998415</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1556832976556203</v>
+        <v>0.1566689997930563</v>
       </c>
       <c r="T18">
-        <v>0.6720325696700808</v>
+        <v>0.6780610012377832</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>23.86936968896235</v>
+        <v>22.4652891190234</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1361064798282367</v>
+        <v>0.1357249096257524</v>
       </c>
       <c r="C19">
-        <v>52.70663015462634</v>
+        <v>52.25532490439953</v>
       </c>
       <c r="D19">
-        <v>54.57208015462634</v>
+        <v>54.72462490439953</v>
       </c>
       <c r="E19">
-        <v>9.580450000000001</v>
+        <v>10.1843</v>
       </c>
       <c r="F19">
-        <v>10.26545</v>
+        <v>10.8693</v>
       </c>
       <c r="G19">
         <v>8.4</v>
@@ -2839,28 +2839,28 @@
         <v>11.6</v>
       </c>
       <c r="M19">
-        <v>0.516352135</v>
+        <v>0.5467257900000001</v>
       </c>
       <c r="N19">
-        <v>11.083647865</v>
+        <v>11.05327421</v>
       </c>
       <c r="O19">
-        <v>3.21425788085</v>
+        <v>3.2054495209</v>
       </c>
       <c r="P19">
-        <v>7.869389984150001</v>
+        <v>7.847824689099999</v>
       </c>
       <c r="Q19">
-        <v>8.46938998415</v>
+        <v>8.447824689099999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1566689997930563</v>
+        <v>0.1576787434460395</v>
       </c>
       <c r="T19">
-        <v>0.6780610012377832</v>
+        <v>0.6842364677217709</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>22.4652891190234</v>
+        <v>21.21721750129987</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1357249096257524</v>
+        <v>0.135343339423268</v>
       </c>
       <c r="C20">
-        <v>52.25532490439953</v>
+        <v>51.80487485811781</v>
       </c>
       <c r="D20">
-        <v>54.72462490439953</v>
+        <v>54.87802485811781</v>
       </c>
       <c r="E20">
-        <v>10.1843</v>
+        <v>10.78815</v>
       </c>
       <c r="F20">
-        <v>10.8693</v>
+        <v>11.47315</v>
       </c>
       <c r="G20">
         <v>8.4</v>
@@ -2921,28 +2921,28 @@
         <v>11.6</v>
       </c>
       <c r="M20">
-        <v>0.54672579</v>
+        <v>0.577099445</v>
       </c>
       <c r="N20">
-        <v>11.05327421</v>
+        <v>11.022900555</v>
       </c>
       <c r="O20">
-        <v>3.2054495209</v>
+        <v>3.19664116095</v>
       </c>
       <c r="P20">
-        <v>7.847824689099999</v>
+        <v>7.82625939405</v>
       </c>
       <c r="Q20">
-        <v>8.447824689099999</v>
+        <v>8.42625939405</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1576787434460395</v>
+        <v>0.1587134190410716</v>
       </c>
       <c r="T20">
-        <v>0.6842364677217709</v>
+        <v>0.6905644148596843</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>21.21721750129987</v>
+        <v>20.10052184333672</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.135343339423268</v>
+        <v>0.1349617692207836</v>
       </c>
       <c r="C21">
-        <v>51.80487485811781</v>
+        <v>51.35528722772732</v>
       </c>
       <c r="D21">
-        <v>54.87802485811781</v>
+        <v>55.03228722772732</v>
       </c>
       <c r="E21">
-        <v>10.78815</v>
+        <v>11.392</v>
       </c>
       <c r="F21">
-        <v>11.47315</v>
+        <v>12.077</v>
       </c>
       <c r="G21">
         <v>8.4</v>
@@ -3003,28 +3003,28 @@
         <v>11.6</v>
       </c>
       <c r="M21">
-        <v>0.577099445</v>
+        <v>0.6074731000000001</v>
       </c>
       <c r="N21">
-        <v>11.022900555</v>
+        <v>10.9925269</v>
       </c>
       <c r="O21">
-        <v>3.19664116095</v>
+        <v>3.187832801</v>
       </c>
       <c r="P21">
-        <v>7.82625939405</v>
+        <v>7.804694099</v>
       </c>
       <c r="Q21">
-        <v>8.42625939405</v>
+        <v>8.404694099</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1587134190410716</v>
+        <v>0.1597739615259795</v>
       </c>
       <c r="T21">
-        <v>0.6905644148596843</v>
+        <v>0.6970505606760455</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>20.10052184333672</v>
+        <v>19.09549575116989</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1349617692207836</v>
+        <v>0.1345801990182993</v>
       </c>
       <c r="C22">
-        <v>51.35528722772732</v>
+        <v>50.90656930649405</v>
       </c>
       <c r="D22">
-        <v>55.03228722772732</v>
+        <v>55.18741930649406</v>
       </c>
       <c r="E22">
-        <v>11.392</v>
+        <v>11.99585</v>
       </c>
       <c r="F22">
-        <v>12.077</v>
+        <v>12.68085</v>
       </c>
       <c r="G22">
         <v>8.4</v>
@@ -3085,28 +3085,28 @@
         <v>11.6</v>
       </c>
       <c r="M22">
-        <v>0.6074731000000001</v>
+        <v>0.6378467550000001</v>
       </c>
       <c r="N22">
-        <v>10.9925269</v>
+        <v>10.962153245</v>
       </c>
       <c r="O22">
-        <v>3.187832801</v>
+        <v>3.17902444105</v>
       </c>
       <c r="P22">
-        <v>7.804694099</v>
+        <v>7.78312880395</v>
       </c>
       <c r="Q22">
-        <v>8.404694099</v>
+        <v>8.383128803949999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1597739615259795</v>
+        <v>0.1608613531877206</v>
       </c>
       <c r="T22">
-        <v>0.6970505606760455</v>
+        <v>0.7037009127156058</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>19.09549575116989</v>
+        <v>18.1861864296856</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1345801990182993</v>
+        <v>0.1341986288158149</v>
       </c>
       <c r="C23">
-        <v>50.90656930649406</v>
+        <v>50.45872847015332</v>
       </c>
       <c r="D23">
-        <v>55.18741930649406</v>
+        <v>55.34342847015333</v>
       </c>
       <c r="E23">
-        <v>11.99585</v>
+        <v>12.5997</v>
       </c>
       <c r="F23">
-        <v>12.68085</v>
+        <v>13.2847</v>
       </c>
       <c r="G23">
         <v>8.4</v>
@@ -3167,28 +3167,28 @@
         <v>11.6</v>
       </c>
       <c r="M23">
-        <v>0.637846755</v>
+        <v>0.66822041</v>
       </c>
       <c r="N23">
-        <v>10.962153245</v>
+        <v>10.93177959</v>
       </c>
       <c r="O23">
-        <v>3.17902444105</v>
+        <v>3.1702160811</v>
       </c>
       <c r="P23">
-        <v>7.78312880395</v>
+        <v>7.7615635089</v>
       </c>
       <c r="Q23">
-        <v>8.383128803949999</v>
+        <v>8.3615635089</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1608613531877206</v>
+        <v>0.1619766266869422</v>
       </c>
       <c r="T23">
-        <v>0.7037009127156058</v>
+        <v>0.7105217866023341</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>18.18618642968561</v>
+        <v>17.35954159197263</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1341986288158149</v>
+        <v>0.1338170586133305</v>
       </c>
       <c r="C24">
-        <v>50.45872847015332</v>
+        <v>50.01177217807855</v>
       </c>
       <c r="D24">
-        <v>55.34342847015333</v>
+        <v>55.50032217807856</v>
       </c>
       <c r="E24">
-        <v>12.5997</v>
+        <v>13.20355</v>
       </c>
       <c r="F24">
-        <v>13.2847</v>
+        <v>13.88855</v>
       </c>
       <c r="G24">
         <v>8.4</v>
@@ -3249,28 +3249,28 @@
         <v>11.6</v>
       </c>
       <c r="M24">
-        <v>0.66822041</v>
+        <v>0.6985940650000001</v>
       </c>
       <c r="N24">
-        <v>10.93177959</v>
+        <v>10.901405935</v>
       </c>
       <c r="O24">
-        <v>3.1702160811</v>
+        <v>3.16140772115</v>
       </c>
       <c r="P24">
-        <v>7.7615635089</v>
+        <v>7.73999821385</v>
       </c>
       <c r="Q24">
-        <v>8.3615635089</v>
+        <v>8.339998213849999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1619766266869422</v>
+        <v>0.1631208683290007</v>
       </c>
       <c r="T24">
-        <v>0.7105217866023341</v>
+        <v>0.7175198260445621</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>17.35954159197263</v>
+        <v>16.60477891406077</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1338170586133305</v>
+        <v>0.1334354884108462</v>
       </c>
       <c r="C25">
-        <v>50.01177217807855</v>
+        <v>49.56570797447041</v>
       </c>
       <c r="D25">
-        <v>55.50032217807856</v>
+        <v>55.65810797447042</v>
       </c>
       <c r="E25">
-        <v>13.20355</v>
+        <v>13.8074</v>
       </c>
       <c r="F25">
-        <v>13.88855</v>
+        <v>14.4924</v>
       </c>
       <c r="G25">
         <v>8.4</v>
@@ -3331,28 +3331,28 @@
         <v>11.6</v>
       </c>
       <c r="M25">
-        <v>0.6985940650000001</v>
+        <v>0.7289677200000001</v>
       </c>
       <c r="N25">
-        <v>10.901405935</v>
+        <v>10.87103228</v>
       </c>
       <c r="O25">
-        <v>3.16140772115</v>
+        <v>3.1525993612</v>
       </c>
       <c r="P25">
-        <v>7.73999821385</v>
+        <v>7.7184329188</v>
       </c>
       <c r="Q25">
-        <v>8.339998213849999</v>
+        <v>8.318432918799999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1631208683290007</v>
+        <v>0.1642952215932186</v>
       </c>
       <c r="T25">
-        <v>0.7175198260445621</v>
+        <v>0.7247020244194802</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>16.60477891406077</v>
+        <v>15.9129131259749</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1334354884108462</v>
+        <v>0.1330539182083618</v>
       </c>
       <c r="C26">
-        <v>49.56570797447041</v>
+        <v>49.12054348956583</v>
       </c>
       <c r="D26">
-        <v>55.65810797447042</v>
+        <v>55.81679348956583</v>
       </c>
       <c r="E26">
-        <v>13.8074</v>
+        <v>14.41125</v>
       </c>
       <c r="F26">
-        <v>14.4924</v>
+        <v>15.09625</v>
       </c>
       <c r="G26">
         <v>8.4</v>
@@ -3413,28 +3413,28 @@
         <v>11.6</v>
       </c>
       <c r="M26">
-        <v>0.72896772</v>
+        <v>0.759341375</v>
       </c>
       <c r="N26">
-        <v>10.87103228</v>
+        <v>10.840658625</v>
       </c>
       <c r="O26">
-        <v>3.1525993612</v>
+        <v>3.14379100125</v>
       </c>
       <c r="P26">
-        <v>7.7184329188</v>
+        <v>7.69686762375</v>
       </c>
       <c r="Q26">
-        <v>8.318432918799999</v>
+        <v>8.29686762375</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1642952215932186</v>
+        <v>0.1655008909444824</v>
       </c>
       <c r="T26">
-        <v>0.7247020244194802</v>
+        <v>0.732075748084396</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>15.91291312597491</v>
+        <v>15.27639660093591</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1330539182083618</v>
+        <v>0.1326723480058774</v>
       </c>
       <c r="C27">
-        <v>49.12054348956583</v>
+        <v>48.67628644086817</v>
       </c>
       <c r="D27">
-        <v>55.81679348956583</v>
+        <v>55.97638644086817</v>
       </c>
       <c r="E27">
-        <v>14.41125</v>
+        <v>15.0151</v>
       </c>
       <c r="F27">
-        <v>15.09625</v>
+        <v>15.7001</v>
       </c>
       <c r="G27">
         <v>8.4</v>
@@ -3495,28 +3495,28 @@
         <v>11.6</v>
       </c>
       <c r="M27">
-        <v>0.759341375</v>
+        <v>0.7897150300000001</v>
       </c>
       <c r="N27">
-        <v>10.840658625</v>
+        <v>10.81028497</v>
       </c>
       <c r="O27">
-        <v>3.14379100125</v>
+        <v>3.1349826413</v>
       </c>
       <c r="P27">
-        <v>7.69686762375</v>
+        <v>7.6753023287</v>
       </c>
       <c r="Q27">
-        <v>8.29686762375</v>
+        <v>8.2753023287</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1655008909444824</v>
+        <v>0.1667391459538884</v>
       </c>
       <c r="T27">
-        <v>0.732075748084396</v>
+        <v>0.7396487615780934</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>15.27639660093591</v>
+        <v>14.6888428855153</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1326723480058774</v>
+        <v>0.132290777803393</v>
       </c>
       <c r="C28">
-        <v>48.67628644086817</v>
+        <v>48.23294463439827</v>
       </c>
       <c r="D28">
-        <v>55.97638644086817</v>
+        <v>56.13689463439827</v>
       </c>
       <c r="E28">
-        <v>15.0151</v>
+        <v>15.61895</v>
       </c>
       <c r="F28">
-        <v>15.7001</v>
+        <v>16.30395</v>
       </c>
       <c r="G28">
         <v>8.4</v>
@@ -3577,28 +3577,28 @@
         <v>11.6</v>
       </c>
       <c r="M28">
-        <v>0.7897150300000001</v>
+        <v>0.8200886850000002</v>
       </c>
       <c r="N28">
-        <v>10.81028497</v>
+        <v>10.779911315</v>
       </c>
       <c r="O28">
-        <v>3.1349826413</v>
+        <v>3.12617428135</v>
       </c>
       <c r="P28">
-        <v>7.6753023287</v>
+        <v>7.65373703365</v>
       </c>
       <c r="Q28">
-        <v>8.2753023287</v>
+        <v>8.253737033649999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1667391459538884</v>
+        <v>0.1680113257580727</v>
       </c>
       <c r="T28">
-        <v>0.7396487615780934</v>
+        <v>0.747429254893536</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>14.6888428855153</v>
+        <v>14.14481166753325</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.132290777803393</v>
+        <v>0.1319092076009087</v>
       </c>
       <c r="C29">
-        <v>48.23294463439827</v>
+        <v>47.79052596596717</v>
       </c>
       <c r="D29">
-        <v>56.13689463439827</v>
+        <v>56.29832596596717</v>
       </c>
       <c r="E29">
-        <v>15.61895</v>
+        <v>16.2228</v>
       </c>
       <c r="F29">
-        <v>16.30395</v>
+        <v>16.9078</v>
       </c>
       <c r="G29">
         <v>8.4</v>
@@ -3659,28 +3659,28 @@
         <v>11.6</v>
       </c>
       <c r="M29">
-        <v>0.8200886850000002</v>
+        <v>0.8504623400000001</v>
       </c>
       <c r="N29">
-        <v>10.779911315</v>
+        <v>10.74953766</v>
       </c>
       <c r="O29">
-        <v>3.12617428135</v>
+        <v>3.1173659214</v>
       </c>
       <c r="P29">
-        <v>7.65373703365</v>
+        <v>7.6321717386</v>
       </c>
       <c r="Q29">
-        <v>8.253737033649999</v>
+        <v>8.2321717386</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1680113257580727</v>
+        <v>0.169318843890151</v>
       </c>
       <c r="T29">
-        <v>0.747429254893536</v>
+        <v>0.7554258730232964</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>14.14481166753325</v>
+        <v>13.6396398222642</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1319092076009087</v>
+        <v>0.1315276373984243</v>
       </c>
       <c r="C30">
-        <v>47.79052596596717</v>
+        <v>47.34903842247098</v>
       </c>
       <c r="D30">
-        <v>56.29832596596717</v>
+        <v>56.46068842247099</v>
       </c>
       <c r="E30">
-        <v>16.2228</v>
+        <v>16.82665</v>
       </c>
       <c r="F30">
-        <v>16.9078</v>
+        <v>17.51165</v>
       </c>
       <c r="G30">
         <v>8.4</v>
@@ -3741,28 +3741,28 @@
         <v>11.6</v>
       </c>
       <c r="M30">
-        <v>0.8504623400000001</v>
+        <v>0.8808359950000001</v>
       </c>
       <c r="N30">
-        <v>10.74953766</v>
+        <v>10.719164005</v>
       </c>
       <c r="O30">
-        <v>3.1173659214</v>
+        <v>3.10855756145</v>
       </c>
       <c r="P30">
-        <v>7.6321717386</v>
+        <v>7.61060644355</v>
       </c>
       <c r="Q30">
-        <v>8.2321717386</v>
+        <v>8.210606443549999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.169318843890151</v>
+        <v>0.1706631935189075</v>
       </c>
       <c r="T30">
-        <v>0.7554258730232964</v>
+        <v>0.7636477480017824</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>13.6396398222642</v>
+        <v>13.16930741459992</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1315276373984243</v>
+        <v>0.13146556719594</v>
       </c>
       <c r="C31">
-        <v>47.34903842247098</v>
+        <v>46.77168860113872</v>
       </c>
       <c r="D31">
-        <v>56.46068842247099</v>
+        <v>56.48718860113871</v>
       </c>
       <c r="E31">
-        <v>16.82665</v>
+        <v>17.4305</v>
       </c>
       <c r="F31">
-        <v>17.51165</v>
+        <v>18.1155</v>
       </c>
       <c r="G31">
         <v>8.4</v>
@@ -3823,45 +3823,45 @@
         <v>11.6</v>
       </c>
       <c r="M31">
-        <v>0.880835995</v>
+        <v>0.9383829</v>
       </c>
       <c r="N31">
-        <v>10.719164005</v>
+        <v>10.6616171</v>
       </c>
       <c r="O31">
-        <v>3.10855756145</v>
+        <v>3.091868959</v>
       </c>
       <c r="P31">
-        <v>7.61060644355</v>
+        <v>7.569748141</v>
       </c>
       <c r="Q31">
-        <v>8.210606443549999</v>
+        <v>8.169748140999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1706631935189075</v>
+        <v>0.1720459531370571</v>
       </c>
       <c r="T31">
-        <v>0.7636477480017824</v>
+        <v>0.7721045336939395</v>
       </c>
       <c r="U31">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V31">
         <v>0.29</v>
       </c>
       <c r="W31">
-        <v>0.03571299999999999</v>
+        <v>0.036778</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y31">
-        <v>13.16930741459992</v>
+        <v>12.36169158666467</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.13146556719594</v>
+        <v>0.1310946469934556</v>
       </c>
       <c r="C32">
-        <v>46.77168860113872</v>
+        <v>46.32671878520014</v>
       </c>
       <c r="D32">
-        <v>56.48718860113871</v>
+        <v>56.64606878520014</v>
       </c>
       <c r="E32">
-        <v>17.4305</v>
+        <v>18.03435</v>
       </c>
       <c r="F32">
-        <v>18.1155</v>
+        <v>18.71935</v>
       </c>
       <c r="G32">
         <v>8.4</v>
@@ -3905,28 +3905,28 @@
         <v>11.6</v>
       </c>
       <c r="M32">
-        <v>0.9383829</v>
+        <v>0.9696623300000001</v>
       </c>
       <c r="N32">
-        <v>10.6616171</v>
+        <v>10.63033767</v>
       </c>
       <c r="O32">
-        <v>3.091868959</v>
+        <v>3.082797924299999</v>
       </c>
       <c r="P32">
-        <v>7.569748141</v>
+        <v>7.5475397457</v>
       </c>
       <c r="Q32">
-        <v>8.169748140999999</v>
+        <v>8.1475397457</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1720459531370571</v>
+        <v>0.1734687927441386</v>
       </c>
       <c r="T32">
-        <v>0.7721045336939395</v>
+        <v>0.7808064436090576</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>12.36169158666467</v>
+        <v>11.96292734193356</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1310946469934556</v>
+        <v>0.1307237267909712</v>
       </c>
       <c r="C33">
-        <v>46.32671878520014</v>
+        <v>45.88264524729998</v>
       </c>
       <c r="D33">
-        <v>56.64606878520014</v>
+        <v>56.80584524729998</v>
       </c>
       <c r="E33">
-        <v>18.03435</v>
+        <v>18.6382</v>
       </c>
       <c r="F33">
-        <v>18.71935</v>
+        <v>19.3232</v>
       </c>
       <c r="G33">
         <v>8.4</v>
@@ -3987,28 +3987,28 @@
         <v>11.6</v>
       </c>
       <c r="M33">
-        <v>0.9696623300000001</v>
+        <v>1.00094176</v>
       </c>
       <c r="N33">
-        <v>10.63033767</v>
+        <v>10.59905824</v>
       </c>
       <c r="O33">
-        <v>3.082797924299999</v>
+        <v>3.0737268896</v>
       </c>
       <c r="P33">
-        <v>7.5475397457</v>
+        <v>7.5253313504</v>
       </c>
       <c r="Q33">
-        <v>8.1475397457</v>
+        <v>8.1253313504</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1734687927441386</v>
+        <v>0.1749334805749577</v>
       </c>
       <c r="T33">
-        <v>0.7808064436090576</v>
+        <v>0.789764292051091</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>11.96292734193356</v>
+        <v>11.58908586249813</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1307237267909712</v>
+        <v>0.1303528065884869</v>
       </c>
       <c r="C34">
-        <v>45.88264524729998</v>
+        <v>45.43947559304276</v>
       </c>
       <c r="D34">
-        <v>56.80584524729998</v>
+        <v>56.96652559304277</v>
       </c>
       <c r="E34">
-        <v>18.6382</v>
+        <v>19.24205</v>
       </c>
       <c r="F34">
-        <v>19.3232</v>
+        <v>19.92705</v>
       </c>
       <c r="G34">
         <v>8.4</v>
@@ -4069,28 +4069,28 @@
         <v>11.6</v>
       </c>
       <c r="M34">
-        <v>1.00094176</v>
+        <v>1.03222119</v>
       </c>
       <c r="N34">
-        <v>10.59905824</v>
+        <v>10.56777881</v>
       </c>
       <c r="O34">
-        <v>3.0737268896</v>
+        <v>3.0646558549</v>
       </c>
       <c r="P34">
-        <v>7.5253313504</v>
+        <v>7.5031229551</v>
       </c>
       <c r="Q34">
-        <v>8.1253313504</v>
+        <v>8.1031229551</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1749334805749577</v>
+        <v>0.1764418904305774</v>
       </c>
       <c r="T34">
-        <v>0.789764292051091</v>
+        <v>0.7989895389540805</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>11.58908586249813</v>
+        <v>11.23790144242243</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1303528065884869</v>
+        <v>0.1299818863860025</v>
       </c>
       <c r="C35">
-        <v>45.43947559304276</v>
+        <v>44.99721751432966</v>
       </c>
       <c r="D35">
-        <v>56.96652559304277</v>
+        <v>57.12811751432966</v>
       </c>
       <c r="E35">
-        <v>19.24205</v>
+        <v>19.8459</v>
       </c>
       <c r="F35">
-        <v>19.92705</v>
+        <v>20.5309</v>
       </c>
       <c r="G35">
         <v>8.4</v>
@@ -4151,28 +4151,28 @@
         <v>11.6</v>
       </c>
       <c r="M35">
-        <v>1.03222119</v>
+        <v>1.06350062</v>
       </c>
       <c r="N35">
-        <v>10.56777881</v>
+        <v>10.53649938</v>
       </c>
       <c r="O35">
-        <v>3.0646558549</v>
+        <v>3.0555848202</v>
       </c>
       <c r="P35">
-        <v>7.5031229551</v>
+        <v>7.480914559799999</v>
       </c>
       <c r="Q35">
-        <v>8.1031229551</v>
+        <v>8.080914559799998</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1764418904305774</v>
+        <v>0.1779960096757614</v>
       </c>
       <c r="T35">
-        <v>0.7989895389540805</v>
+        <v>0.8084943387935244</v>
       </c>
       <c r="U35">
         <v>0.0518</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>11.23790144242243</v>
+        <v>10.90737492941001</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1299818863860025</v>
+        <v>0.1296109661835181</v>
       </c>
       <c r="C36">
-        <v>44.99721751432966</v>
+        <v>44.55587879058582</v>
       </c>
       <c r="D36">
-        <v>57.12811751432966</v>
+        <v>57.29062879058581</v>
       </c>
       <c r="E36">
-        <v>19.8459</v>
+        <v>20.44975000000001</v>
       </c>
       <c r="F36">
-        <v>20.5309</v>
+        <v>21.13475</v>
       </c>
       <c r="G36">
         <v>8.4</v>
@@ -4233,28 +4233,28 @@
         <v>11.6</v>
       </c>
       <c r="M36">
-        <v>1.06350062</v>
+        <v>1.09478005</v>
       </c>
       <c r="N36">
-        <v>10.53649938</v>
+        <v>10.50521995</v>
       </c>
       <c r="O36">
-        <v>3.0555848202</v>
+        <v>3.046513785499999</v>
       </c>
       <c r="P36">
-        <v>7.480914559799999</v>
+        <v>7.4587061645</v>
       </c>
       <c r="Q36">
-        <v>8.080914559799998</v>
+        <v>8.058706164499998</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1779960096757614</v>
+        <v>0.1795979479746433</v>
       </c>
       <c r="T36">
-        <v>0.8084943387935244</v>
+        <v>0.8182915940126435</v>
       </c>
       <c r="U36">
         <v>0.0518</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>10.90737492941001</v>
+        <v>10.59573564571258</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1296109661835181</v>
+        <v>0.1292400459810338</v>
       </c>
       <c r="C37">
-        <v>44.55587879058582</v>
+        <v>44.11546729000889</v>
       </c>
       <c r="D37">
-        <v>57.29062879058581</v>
+        <v>57.4540672900089</v>
       </c>
       <c r="E37">
-        <v>20.44975000000001</v>
+        <v>21.05360000000001</v>
       </c>
       <c r="F37">
-        <v>21.13475</v>
+        <v>21.73860000000001</v>
       </c>
       <c r="G37">
         <v>8.4</v>
@@ -4315,28 +4315,28 @@
         <v>11.6</v>
       </c>
       <c r="M37">
-        <v>1.09478005</v>
+        <v>1.12605948</v>
       </c>
       <c r="N37">
-        <v>10.50521995</v>
+        <v>10.47394052</v>
       </c>
       <c r="O37">
-        <v>3.046513785499999</v>
+        <v>3.037442750799999</v>
       </c>
       <c r="P37">
-        <v>7.4587061645</v>
+        <v>7.4364977692</v>
       </c>
       <c r="Q37">
-        <v>8.058706164499998</v>
+        <v>8.0364977692</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1795979479746433</v>
+        <v>0.1812499468453653</v>
       </c>
       <c r="T37">
-        <v>0.8182915940126435</v>
+        <v>0.8283950134573599</v>
       </c>
       <c r="U37">
         <v>0.0518</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>10.59573564571258</v>
+        <v>10.30140965555389</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1292400459810338</v>
+        <v>0.1288691257785494</v>
       </c>
       <c r="C38">
-        <v>44.11546729000888</v>
+        <v>43.67599097083884</v>
       </c>
       <c r="D38">
-        <v>57.45406729000889</v>
+        <v>57.61844097083883</v>
       </c>
       <c r="E38">
-        <v>21.0536</v>
+        <v>21.65745</v>
       </c>
       <c r="F38">
-        <v>21.7386</v>
+        <v>22.34245</v>
       </c>
       <c r="G38">
         <v>8.4</v>
@@ -4397,28 +4397,28 @@
         <v>11.6</v>
       </c>
       <c r="M38">
-        <v>1.12605948</v>
+        <v>1.15733891</v>
       </c>
       <c r="N38">
-        <v>10.47394052</v>
+        <v>10.44266109</v>
       </c>
       <c r="O38">
-        <v>3.037442750799999</v>
+        <v>3.0283717161</v>
       </c>
       <c r="P38">
-        <v>7.4364977692</v>
+        <v>7.4142893739</v>
       </c>
       <c r="Q38">
-        <v>8.0364977692</v>
+        <v>8.014289373899999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1812499468453653</v>
+        <v>0.1829543901246816</v>
       </c>
       <c r="T38">
-        <v>0.8283950134573599</v>
+        <v>0.8388191763765118</v>
       </c>
       <c r="U38">
         <v>0.0518</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>10.3014096555539</v>
+        <v>10.02299317837676</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1288691257785494</v>
+        <v>0.1289568655760651</v>
       </c>
       <c r="C39">
-        <v>43.67599097083884</v>
+        <v>43.03317411763484</v>
       </c>
       <c r="D39">
-        <v>57.61844097083883</v>
+        <v>57.57947411763483</v>
       </c>
       <c r="E39">
-        <v>21.65745</v>
+        <v>22.2613</v>
       </c>
       <c r="F39">
-        <v>22.34245</v>
+        <v>22.9463</v>
       </c>
       <c r="G39">
         <v>8.4</v>
@@ -4479,45 +4479,45 @@
         <v>11.6</v>
       </c>
       <c r="M39">
-        <v>1.15733891</v>
+        <v>1.22762705</v>
       </c>
       <c r="N39">
-        <v>10.44266109</v>
+        <v>10.37237295</v>
       </c>
       <c r="O39">
-        <v>3.0283717161</v>
+        <v>3.0079881555</v>
       </c>
       <c r="P39">
-        <v>7.4142893739</v>
+        <v>7.364384794499999</v>
       </c>
       <c r="Q39">
-        <v>8.014289373899999</v>
+        <v>7.964384794499999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1829543901246816</v>
+        <v>0.1847138154452662</v>
       </c>
       <c r="T39">
-        <v>0.8388191763765118</v>
+        <v>0.8495796026156364</v>
       </c>
       <c r="U39">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V39">
         <v>0.29</v>
       </c>
       <c r="W39">
-        <v>0.036778</v>
+        <v>0.037985</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y39">
-        <v>10.02299317837676</v>
+        <v>9.449123819811563</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1289568655760651</v>
+        <v>0.1285980153735807</v>
       </c>
       <c r="C40">
-        <v>43.03317411763484</v>
+        <v>42.58903003667743</v>
       </c>
       <c r="D40">
-        <v>57.57947411763483</v>
+        <v>57.73918003667742</v>
       </c>
       <c r="E40">
-        <v>22.2613</v>
+        <v>22.86515</v>
       </c>
       <c r="F40">
-        <v>22.9463</v>
+        <v>23.55015</v>
       </c>
       <c r="G40">
         <v>8.4</v>
@@ -4561,28 +4561,28 @@
         <v>11.6</v>
       </c>
       <c r="M40">
-        <v>1.22762705</v>
+        <v>1.259933025</v>
       </c>
       <c r="N40">
-        <v>10.37237295</v>
+        <v>10.340066975</v>
       </c>
       <c r="O40">
-        <v>3.0079881555</v>
+        <v>2.99861942275</v>
       </c>
       <c r="P40">
-        <v>7.364384794499999</v>
+        <v>7.341447552249999</v>
       </c>
       <c r="Q40">
-        <v>7.964384794499999</v>
+        <v>7.941447552249999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1847138154452662</v>
+        <v>0.1865309268419355</v>
       </c>
       <c r="T40">
-        <v>0.8495796026156364</v>
+        <v>0.8606928297150601</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>9.449123819811563</v>
+        <v>9.206838593662548</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1285980153735807</v>
+        <v>0.1282391651710963</v>
       </c>
       <c r="C41">
-        <v>42.58903003667743</v>
+        <v>42.14577435988385</v>
       </c>
       <c r="D41">
-        <v>57.73918003667742</v>
+        <v>57.89977435988385</v>
       </c>
       <c r="E41">
-        <v>22.86515</v>
+        <v>23.469</v>
       </c>
       <c r="F41">
-        <v>23.55015</v>
+        <v>24.154</v>
       </c>
       <c r="G41">
         <v>8.4</v>
@@ -4643,28 +4643,28 @@
         <v>11.6</v>
       </c>
       <c r="M41">
-        <v>1.259933025</v>
+        <v>1.292239</v>
       </c>
       <c r="N41">
-        <v>10.340066975</v>
+        <v>10.307761</v>
       </c>
       <c r="O41">
-        <v>2.99861942275</v>
+        <v>2.98925069</v>
       </c>
       <c r="P41">
-        <v>7.341447552249999</v>
+        <v>7.31851031</v>
       </c>
       <c r="Q41">
-        <v>7.941447552249999</v>
+        <v>7.918510309999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1865309268419355</v>
+        <v>0.1884086086184939</v>
       </c>
       <c r="T41">
-        <v>0.8606928297150601</v>
+        <v>0.872176497717798</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>9.206838593662548</v>
+        <v>8.976667628820984</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1282391651710963</v>
+        <v>0.1278803149686119</v>
       </c>
       <c r="C42">
-        <v>42.14577435988385</v>
+        <v>41.70341452088576</v>
       </c>
       <c r="D42">
-        <v>57.89977435988385</v>
+        <v>58.06126452088576</v>
       </c>
       <c r="E42">
-        <v>23.469</v>
+        <v>24.07285000000001</v>
       </c>
       <c r="F42">
-        <v>24.154</v>
+        <v>24.75785</v>
       </c>
       <c r="G42">
         <v>8.4</v>
@@ -4725,28 +4725,28 @@
         <v>11.6</v>
       </c>
       <c r="M42">
-        <v>1.292239</v>
+        <v>1.324544975</v>
       </c>
       <c r="N42">
-        <v>10.307761</v>
+        <v>10.275455025</v>
       </c>
       <c r="O42">
-        <v>2.98925069</v>
+        <v>2.979881957249999</v>
       </c>
       <c r="P42">
-        <v>7.31851031</v>
+        <v>7.29557306775</v>
       </c>
       <c r="Q42">
-        <v>7.918510309999999</v>
+        <v>7.89557306775</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1884086086184939</v>
+        <v>0.190349940624766</v>
       </c>
       <c r="T42">
-        <v>0.872176497717798</v>
+        <v>0.8840494426019846</v>
       </c>
       <c r="U42">
         <v>0.0535</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>8.976667628820984</v>
+        <v>8.757724515922909</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1278803149686119</v>
+        <v>0.1275214647661276</v>
       </c>
       <c r="C43">
-        <v>41.70341452088576</v>
+        <v>41.26195803648029</v>
       </c>
       <c r="D43">
-        <v>58.06126452088576</v>
+        <v>58.22365803648029</v>
       </c>
       <c r="E43">
-        <v>24.07285000000001</v>
+        <v>24.67670000000001</v>
       </c>
       <c r="F43">
-        <v>24.75785</v>
+        <v>25.36170000000001</v>
       </c>
       <c r="G43">
         <v>8.4</v>
@@ -4807,28 +4807,28 @@
         <v>11.6</v>
       </c>
       <c r="M43">
-        <v>1.324544975</v>
+        <v>1.35685095</v>
       </c>
       <c r="N43">
-        <v>10.275455025</v>
+        <v>10.24314905</v>
       </c>
       <c r="O43">
-        <v>2.979881957249999</v>
+        <v>2.970513224499999</v>
       </c>
       <c r="P43">
-        <v>7.29557306775</v>
+        <v>7.2726358255</v>
       </c>
       <c r="Q43">
-        <v>7.89557306775</v>
+        <v>7.8726358255</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.190349940624766</v>
+        <v>0.1923582151140131</v>
       </c>
       <c r="T43">
-        <v>0.8840494426019846</v>
+        <v>0.8963317993787293</v>
       </c>
       <c r="U43">
         <v>0.0535</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>8.757724515922909</v>
+        <v>8.549207265543792</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1275214647661276</v>
+        <v>0.1271626145636432</v>
       </c>
       <c r="C44">
-        <v>41.26195803648029</v>
+        <v>40.82141250779637</v>
       </c>
       <c r="D44">
-        <v>58.22365803648029</v>
+        <v>58.38696250779637</v>
       </c>
       <c r="E44">
-        <v>24.6767</v>
+        <v>25.28055</v>
       </c>
       <c r="F44">
-        <v>25.3617</v>
+        <v>25.96555</v>
       </c>
       <c r="G44">
         <v>8.4</v>
@@ -4889,28 +4889,28 @@
         <v>11.6</v>
       </c>
       <c r="M44">
-        <v>1.35685095</v>
+        <v>1.389156925</v>
       </c>
       <c r="N44">
-        <v>10.24314905</v>
+        <v>10.210843075</v>
       </c>
       <c r="O44">
-        <v>2.970513224499999</v>
+        <v>2.96114449175</v>
       </c>
       <c r="P44">
-        <v>7.2726358255</v>
+        <v>7.24969858325</v>
       </c>
       <c r="Q44">
-        <v>7.8726358255</v>
+        <v>7.849698583249999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1923582151140131</v>
+        <v>0.1944369553748126</v>
       </c>
       <c r="T44">
-        <v>0.8963317993787293</v>
+        <v>0.9090451160423774</v>
       </c>
       <c r="U44">
         <v>0.0535</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>8.549207265543794</v>
+        <v>8.350388491926497</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1271626145636432</v>
+        <v>0.1268037643611589</v>
       </c>
       <c r="C45">
-        <v>40.82141250779637</v>
+        <v>40.38178562148074</v>
       </c>
       <c r="D45">
-        <v>58.38696250779637</v>
+        <v>58.55118562148075</v>
       </c>
       <c r="E45">
-        <v>25.28055</v>
+        <v>25.8844</v>
       </c>
       <c r="F45">
-        <v>25.96555</v>
+        <v>26.5694</v>
       </c>
       <c r="G45">
         <v>8.4</v>
@@ -4971,28 +4971,28 @@
         <v>11.6</v>
       </c>
       <c r="M45">
-        <v>1.389156925</v>
+        <v>1.4214629</v>
       </c>
       <c r="N45">
-        <v>10.210843075</v>
+        <v>10.1785371</v>
       </c>
       <c r="O45">
-        <v>2.96114449175</v>
+        <v>2.951775759</v>
       </c>
       <c r="P45">
-        <v>7.24969858325</v>
+        <v>7.226761341</v>
       </c>
       <c r="Q45">
-        <v>7.849698583249999</v>
+        <v>7.826761340999999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1944369553748126</v>
+        <v>0.1965899363592122</v>
       </c>
       <c r="T45">
-        <v>0.9090451160423774</v>
+        <v>0.9222124797297272</v>
       </c>
       <c r="U45">
         <v>0.0535</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>8.350388491926497</v>
+        <v>8.160606935291803</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1268037643611589</v>
+        <v>0.1264449141586745</v>
       </c>
       <c r="C46">
-        <v>40.38178562148074</v>
+        <v>39.94308515090406</v>
       </c>
       <c r="D46">
-        <v>58.55118562148075</v>
+        <v>58.71633515090406</v>
       </c>
       <c r="E46">
-        <v>25.8844</v>
+        <v>26.48825</v>
       </c>
       <c r="F46">
-        <v>26.5694</v>
+        <v>27.17325</v>
       </c>
       <c r="G46">
         <v>8.4</v>
@@ -5053,28 +5053,28 @@
         <v>11.6</v>
       </c>
       <c r="M46">
-        <v>1.4214629</v>
+        <v>1.453768875</v>
       </c>
       <c r="N46">
-        <v>10.1785371</v>
+        <v>10.146231125</v>
       </c>
       <c r="O46">
-        <v>2.951775759</v>
+        <v>2.94240702625</v>
       </c>
       <c r="P46">
-        <v>7.226761341</v>
+        <v>7.20382409875</v>
       </c>
       <c r="Q46">
-        <v>7.826761340999999</v>
+        <v>7.80382409875</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1965899363592122</v>
+        <v>0.1988212075612263</v>
       </c>
       <c r="T46">
-        <v>0.9222124797297272</v>
+        <v>0.9358586566420716</v>
       </c>
       <c r="U46">
         <v>0.0535</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>8.160606935291803</v>
+        <v>7.97926011450754</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1264449141586745</v>
+        <v>0.1260860639561901</v>
       </c>
       <c r="C47">
-        <v>39.94308515090406</v>
+        <v>39.5053189573872</v>
       </c>
       <c r="D47">
-        <v>58.71633515090406</v>
+        <v>58.88241895738721</v>
       </c>
       <c r="E47">
-        <v>26.48825</v>
+        <v>27.09210000000001</v>
       </c>
       <c r="F47">
-        <v>27.17325</v>
+        <v>27.7771</v>
       </c>
       <c r="G47">
         <v>8.4</v>
@@ -5135,28 +5135,28 @@
         <v>11.6</v>
       </c>
       <c r="M47">
-        <v>1.453768875</v>
+        <v>1.48607485</v>
       </c>
       <c r="N47">
-        <v>10.146231125</v>
+        <v>10.11392515</v>
       </c>
       <c r="O47">
-        <v>2.94240702625</v>
+        <v>2.9330382935</v>
       </c>
       <c r="P47">
-        <v>7.20382409875</v>
+        <v>7.180886856500001</v>
       </c>
       <c r="Q47">
-        <v>7.80382409875</v>
+        <v>7.7808868565</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1988212075612263</v>
+        <v>0.2011351184373891</v>
       </c>
       <c r="T47">
-        <v>0.9358586566420716</v>
+        <v>0.9500102475141324</v>
       </c>
       <c r="U47">
         <v>0.0535</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>7.97926011450754</v>
+        <v>7.805797938105203</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1260860639561901</v>
+        <v>0.1257272137537058</v>
       </c>
       <c r="C48">
-        <v>39.5053189573872</v>
+        <v>39.06849499144898</v>
       </c>
       <c r="D48">
-        <v>58.88241895738721</v>
+        <v>59.04944499144898</v>
       </c>
       <c r="E48">
-        <v>27.09210000000001</v>
+        <v>27.69595000000001</v>
       </c>
       <c r="F48">
-        <v>27.7771</v>
+        <v>28.38095000000001</v>
       </c>
       <c r="G48">
         <v>8.4</v>
@@ -5217,28 +5217,28 @@
         <v>11.6</v>
       </c>
       <c r="M48">
-        <v>1.48607485</v>
+        <v>1.518380825</v>
       </c>
       <c r="N48">
-        <v>10.11392515</v>
+        <v>10.081619175</v>
       </c>
       <c r="O48">
-        <v>2.9330382935</v>
+        <v>2.92366956075</v>
       </c>
       <c r="P48">
-        <v>7.180886856500001</v>
+        <v>7.157949614250001</v>
       </c>
       <c r="Q48">
-        <v>7.7808868565</v>
+        <v>7.75794961425</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2011351184373891</v>
+        <v>0.2035363467051052</v>
       </c>
       <c r="T48">
-        <v>0.9500102475141324</v>
+        <v>0.9646958606832521</v>
       </c>
       <c r="U48">
         <v>0.0535</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>7.805797938105203</v>
+        <v>7.639717130911475</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1257272137537058</v>
+        <v>0.1256410035512214</v>
       </c>
       <c r="C49">
-        <v>39.06849499144898</v>
+        <v>38.50491260326831</v>
       </c>
       <c r="D49">
-        <v>59.04944499144898</v>
+        <v>59.08971260326831</v>
       </c>
       <c r="E49">
-        <v>27.69595000000001</v>
+        <v>28.2998</v>
       </c>
       <c r="F49">
-        <v>28.38095000000001</v>
+        <v>28.9848</v>
       </c>
       <c r="G49">
         <v>8.4</v>
@@ -5299,45 +5299,45 @@
         <v>11.6</v>
       </c>
       <c r="M49">
-        <v>1.518380825</v>
+        <v>1.57387464</v>
       </c>
       <c r="N49">
-        <v>10.081619175</v>
+        <v>10.02612536</v>
       </c>
       <c r="O49">
-        <v>2.92366956075</v>
+        <v>2.9075763544</v>
       </c>
       <c r="P49">
-        <v>7.157949614250001</v>
+        <v>7.1185490056</v>
       </c>
       <c r="Q49">
-        <v>7.75794961425</v>
+        <v>7.7185490056</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2035363467051052</v>
+        <v>0.206029929906195</v>
       </c>
       <c r="T49">
-        <v>0.9646958606832521</v>
+        <v>0.9799463051281072</v>
       </c>
       <c r="U49">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V49">
         <v>0.29</v>
       </c>
       <c r="W49">
-        <v>0.037985</v>
+        <v>0.038553</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y49">
-        <v>7.639717130911475</v>
+        <v>7.37034558228856</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1256410035512214</v>
+        <v>0.125287833348737</v>
       </c>
       <c r="C50">
-        <v>38.50491260326832</v>
+        <v>38.066598530782</v>
       </c>
       <c r="D50">
-        <v>59.08971260326832</v>
+        <v>59.255248530782</v>
       </c>
       <c r="E50">
-        <v>28.2998</v>
+        <v>28.90365</v>
       </c>
       <c r="F50">
-        <v>28.9848</v>
+        <v>29.58865</v>
       </c>
       <c r="G50">
         <v>8.4</v>
@@ -5381,28 +5381,28 @@
         <v>11.6</v>
       </c>
       <c r="M50">
-        <v>1.57387464</v>
+        <v>1.606663695</v>
       </c>
       <c r="N50">
-        <v>10.02612536</v>
+        <v>9.993336305</v>
       </c>
       <c r="O50">
-        <v>2.9075763544</v>
+        <v>2.89806752845</v>
       </c>
       <c r="P50">
-        <v>7.1185490056</v>
+        <v>7.09526877655</v>
       </c>
       <c r="Q50">
-        <v>7.7185490056</v>
+        <v>7.69526877655</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.206029929906195</v>
+        <v>0.2086213006837981</v>
       </c>
       <c r="T50">
-        <v>0.9799463051281072</v>
+        <v>0.9957948062178585</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>7.370345582288561</v>
+        <v>7.219930366323488</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.125287833348737</v>
+        <v>0.1249346631462527</v>
       </c>
       <c r="C51">
-        <v>38.066598530782</v>
+        <v>37.62921453979512</v>
       </c>
       <c r="D51">
-        <v>59.255248530782</v>
+        <v>59.42171453979512</v>
       </c>
       <c r="E51">
-        <v>28.90365</v>
+        <v>29.5075</v>
       </c>
       <c r="F51">
-        <v>29.58865</v>
+        <v>30.1925</v>
       </c>
       <c r="G51">
         <v>8.4</v>
@@ -5463,28 +5463,28 @@
         <v>11.6</v>
       </c>
       <c r="M51">
-        <v>1.606663695</v>
+        <v>1.63945275</v>
       </c>
       <c r="N51">
-        <v>9.993336305</v>
+        <v>9.960547249999999</v>
       </c>
       <c r="O51">
-        <v>2.89806752845</v>
+        <v>2.8885587025</v>
       </c>
       <c r="P51">
-        <v>7.09526877655</v>
+        <v>7.0719885475</v>
       </c>
       <c r="Q51">
-        <v>7.69526877655</v>
+        <v>7.6719885475</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2086213006837981</v>
+        <v>0.2113163262925053</v>
       </c>
       <c r="T51">
-        <v>0.9957948062178585</v>
+        <v>1.0122772473512</v>
       </c>
       <c r="U51">
         <v>0.0543</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>7.219930366323488</v>
+        <v>7.075531758997018</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1249346631462527</v>
+        <v>0.1245814929437683</v>
       </c>
       <c r="C52">
-        <v>37.62921453979512</v>
+        <v>37.19276849103598</v>
       </c>
       <c r="D52">
-        <v>59.42171453979512</v>
+        <v>59.58911849103598</v>
       </c>
       <c r="E52">
-        <v>29.5075</v>
+        <v>30.11135000000001</v>
       </c>
       <c r="F52">
-        <v>30.1925</v>
+        <v>30.79635</v>
       </c>
       <c r="G52">
         <v>8.4</v>
@@ -5545,28 +5545,28 @@
         <v>11.6</v>
       </c>
       <c r="M52">
-        <v>1.63945275</v>
+        <v>1.672241805</v>
       </c>
       <c r="N52">
-        <v>9.960547249999999</v>
+        <v>9.927758194999999</v>
       </c>
       <c r="O52">
-        <v>2.8885587025</v>
+        <v>2.879049876549999</v>
       </c>
       <c r="P52">
-        <v>7.0719885475</v>
+        <v>7.04870831845</v>
       </c>
       <c r="Q52">
-        <v>7.6719885475</v>
+        <v>7.64870831845</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2113163262925053</v>
+        <v>0.2141213529464659</v>
       </c>
       <c r="T52">
-        <v>1.0122772473512</v>
+        <v>1.029432441183861</v>
       </c>
       <c r="U52">
         <v>0.0543</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>7.075531758997018</v>
+        <v>6.936795842153939</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1245814929437683</v>
+        <v>0.1242283227412839</v>
       </c>
       <c r="C53">
-        <v>37.19276849103598</v>
+        <v>36.75726833406473</v>
       </c>
       <c r="D53">
-        <v>59.58911849103598</v>
+        <v>59.75746833406473</v>
       </c>
       <c r="E53">
-        <v>30.11135000000001</v>
+        <v>30.71520000000001</v>
       </c>
       <c r="F53">
-        <v>30.79635</v>
+        <v>31.40020000000001</v>
       </c>
       <c r="G53">
         <v>8.4</v>
@@ -5627,28 +5627,28 @@
         <v>11.6</v>
       </c>
       <c r="M53">
-        <v>1.672241805</v>
+        <v>1.70503086</v>
       </c>
       <c r="N53">
-        <v>9.927758194999999</v>
+        <v>9.894969139999999</v>
       </c>
       <c r="O53">
-        <v>2.879049876549999</v>
+        <v>2.8695410506</v>
       </c>
       <c r="P53">
-        <v>7.04870831845</v>
+        <v>7.025428089399999</v>
       </c>
       <c r="Q53">
-        <v>7.64870831845</v>
+        <v>7.625428089399999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2141213529464659</v>
+        <v>0.2170432557110082</v>
       </c>
       <c r="T53">
-        <v>1.029432441183861</v>
+        <v>1.047302434759551</v>
       </c>
       <c r="U53">
         <v>0.0543</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>6.936795842153939</v>
+        <v>6.803395922112516</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1242283227412839</v>
+        <v>0.1238751525387996</v>
       </c>
       <c r="C54">
-        <v>36.75726833406473</v>
+        <v>36.32272210853168</v>
       </c>
       <c r="D54">
-        <v>59.75746833406473</v>
+        <v>59.92677210853168</v>
       </c>
       <c r="E54">
-        <v>30.71520000000001</v>
+        <v>31.31905000000001</v>
       </c>
       <c r="F54">
-        <v>31.40020000000001</v>
+        <v>32.00405000000001</v>
       </c>
       <c r="G54">
         <v>8.4</v>
@@ -5709,28 +5709,28 @@
         <v>11.6</v>
       </c>
       <c r="M54">
-        <v>1.70503086</v>
+        <v>1.737819915</v>
       </c>
       <c r="N54">
-        <v>9.894969139999999</v>
+        <v>9.862180084999999</v>
       </c>
       <c r="O54">
-        <v>2.8695410506</v>
+        <v>2.860032224649999</v>
       </c>
       <c r="P54">
-        <v>7.025428089399999</v>
+        <v>7.002147860349999</v>
       </c>
       <c r="Q54">
-        <v>7.625428089399999</v>
+        <v>7.602147860349999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2170432557110082</v>
+        <v>0.2200894947634033</v>
       </c>
       <c r="T54">
-        <v>1.047302434759551</v>
+        <v>1.06593285359378</v>
       </c>
       <c r="U54">
         <v>0.0543</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>6.803395922112516</v>
+        <v>6.67502996131794</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1238751525387996</v>
+        <v>0.1235219823363152</v>
       </c>
       <c r="C55">
-        <v>36.32272210853168</v>
+        <v>35.88913794545719</v>
       </c>
       <c r="D55">
-        <v>59.92677210853168</v>
+        <v>60.0970379454572</v>
       </c>
       <c r="E55">
-        <v>31.31905000000001</v>
+        <v>31.92290000000001</v>
       </c>
       <c r="F55">
-        <v>32.00405000000001</v>
+        <v>32.60790000000001</v>
       </c>
       <c r="G55">
         <v>8.4</v>
@@ -5791,28 +5791,28 @@
         <v>11.6</v>
       </c>
       <c r="M55">
-        <v>1.737819915</v>
+        <v>1.770608970000001</v>
       </c>
       <c r="N55">
-        <v>9.862180084999999</v>
+        <v>9.82939103</v>
       </c>
       <c r="O55">
-        <v>2.860032224649999</v>
+        <v>2.8505233987</v>
       </c>
       <c r="P55">
-        <v>7.002147860349999</v>
+        <v>6.9788676313</v>
       </c>
       <c r="Q55">
-        <v>7.602147860349999</v>
+        <v>7.5788676313</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2200894947634033</v>
+        <v>0.2232681789919896</v>
       </c>
       <c r="T55">
-        <v>1.06593285359378</v>
+        <v>1.085373290638192</v>
       </c>
       <c r="U55">
         <v>0.0543</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>6.67502996131794</v>
+        <v>6.551418295367609</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1235219823363152</v>
+        <v>0.1231688121338308</v>
       </c>
       <c r="C56">
-        <v>35.88913794545719</v>
+        <v>35.45652406853339</v>
       </c>
       <c r="D56">
-        <v>60.0970379454572</v>
+        <v>60.26827406853339</v>
       </c>
       <c r="E56">
-        <v>31.92290000000001</v>
+        <v>32.52675</v>
       </c>
       <c r="F56">
-        <v>32.60790000000001</v>
+        <v>33.21175</v>
       </c>
       <c r="G56">
         <v>8.4</v>
@@ -5873,28 +5873,28 @@
         <v>11.6</v>
       </c>
       <c r="M56">
-        <v>1.770608970000001</v>
+        <v>1.803398025</v>
       </c>
       <c r="N56">
-        <v>9.82939103</v>
+        <v>9.796601975</v>
       </c>
       <c r="O56">
-        <v>2.8505233987</v>
+        <v>2.84101457275</v>
       </c>
       <c r="P56">
-        <v>6.9788676313</v>
+        <v>6.95558740225</v>
       </c>
       <c r="Q56">
-        <v>7.5788676313</v>
+        <v>7.55558740225</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2232681789919896</v>
+        <v>0.2265881380751796</v>
       </c>
       <c r="T56">
-        <v>1.085373290638192</v>
+        <v>1.105677747106801</v>
       </c>
       <c r="U56">
         <v>0.0543</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>6.551418295367609</v>
+        <v>6.432301599088198</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1231688121338308</v>
+        <v>0.1228156419313465</v>
       </c>
       <c r="C57">
-        <v>35.45652406853339</v>
+        <v>35.02488879544813</v>
       </c>
       <c r="D57">
-        <v>60.26827406853339</v>
+        <v>60.44048879544814</v>
       </c>
       <c r="E57">
-        <v>32.52675</v>
+        <v>33.1306</v>
       </c>
       <c r="F57">
-        <v>33.21175</v>
+        <v>33.8156</v>
       </c>
       <c r="G57">
         <v>8.4</v>
@@ -5955,28 +5955,28 @@
         <v>11.6</v>
       </c>
       <c r="M57">
-        <v>1.803398025</v>
+        <v>1.83618708</v>
       </c>
       <c r="N57">
-        <v>9.796601975</v>
+        <v>9.763812919999999</v>
       </c>
       <c r="O57">
-        <v>2.84101457275</v>
+        <v>2.8315057468</v>
       </c>
       <c r="P57">
-        <v>6.95558740225</v>
+        <v>6.9323071732</v>
       </c>
       <c r="Q57">
-        <v>7.55558740225</v>
+        <v>7.5323071732</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2265881380751796</v>
+        <v>0.2300590043894238</v>
       </c>
       <c r="T57">
-        <v>1.105677747106801</v>
+        <v>1.126905133414893</v>
       </c>
       <c r="U57">
         <v>0.0543</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>6.432301599088198</v>
+        <v>6.317439070533052</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1228156419313465</v>
+        <v>0.1224624717288621</v>
       </c>
       <c r="C58">
-        <v>35.02488879544813</v>
+        <v>34.59424053923193</v>
       </c>
       <c r="D58">
-        <v>60.44048879544814</v>
+        <v>60.61369053923192</v>
       </c>
       <c r="E58">
-        <v>33.1306</v>
+        <v>33.73445</v>
       </c>
       <c r="F58">
-        <v>33.8156</v>
+        <v>34.41945</v>
       </c>
       <c r="G58">
         <v>8.4</v>
@@ -6037,28 +6037,28 @@
         <v>11.6</v>
       </c>
       <c r="M58">
-        <v>1.83618708</v>
+        <v>1.868976135</v>
       </c>
       <c r="N58">
-        <v>9.763812919999999</v>
+        <v>9.731023864999999</v>
       </c>
       <c r="O58">
-        <v>2.8315057468</v>
+        <v>2.82199692085</v>
       </c>
       <c r="P58">
-        <v>6.9323071732</v>
+        <v>6.90902694415</v>
       </c>
       <c r="Q58">
-        <v>7.5323071732</v>
+        <v>7.509026944149999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2300590043894238</v>
+        <v>0.233691306346191</v>
       </c>
       <c r="T58">
-        <v>1.126905133414893</v>
+        <v>1.149119840016383</v>
       </c>
       <c r="U58">
         <v>0.0543</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>6.317439070533052</v>
+        <v>6.206606806137735</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1224624717288621</v>
+        <v>0.1225211015263777</v>
       </c>
       <c r="C59">
-        <v>34.59424053923193</v>
+        <v>33.96156862624737</v>
       </c>
       <c r="D59">
-        <v>60.61369053923192</v>
+        <v>60.58486862624737</v>
       </c>
       <c r="E59">
-        <v>33.73445</v>
+        <v>34.3383</v>
       </c>
       <c r="F59">
-        <v>34.41945</v>
+        <v>35.02330000000001</v>
       </c>
       <c r="G59">
         <v>8.4</v>
@@ -6119,45 +6119,45 @@
         <v>11.6</v>
       </c>
       <c r="M59">
-        <v>1.868976135</v>
+        <v>1.93678849</v>
       </c>
       <c r="N59">
-        <v>9.731023864999999</v>
+        <v>9.66321151</v>
       </c>
       <c r="O59">
-        <v>2.82199692085</v>
+        <v>2.8023313379</v>
       </c>
       <c r="P59">
-        <v>6.90902694415</v>
+        <v>6.8608801721</v>
       </c>
       <c r="Q59">
-        <v>7.509026944149999</v>
+        <v>7.4608801721</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.233691306346191</v>
+        <v>0.2374965750628042</v>
       </c>
       <c r="T59">
-        <v>1.149119840016383</v>
+        <v>1.172392389789374</v>
       </c>
       <c r="U59">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V59">
         <v>0.29</v>
       </c>
       <c r="W59">
-        <v>0.038553</v>
+        <v>0.039263</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y59">
-        <v>6.206606806137735</v>
+        <v>5.989296229243906</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1225211015263777</v>
+        <v>0.1221750313238934</v>
       </c>
       <c r="C60">
-        <v>33.96156862624738</v>
+        <v>33.52824152708301</v>
       </c>
       <c r="D60">
-        <v>60.58486862624737</v>
+        <v>60.75539152708301</v>
       </c>
       <c r="E60">
-        <v>34.3383</v>
+        <v>34.94215</v>
       </c>
       <c r="F60">
-        <v>35.0233</v>
+        <v>35.62715</v>
       </c>
       <c r="G60">
         <v>8.4</v>
@@ -6201,28 +6201,28 @@
         <v>11.6</v>
       </c>
       <c r="M60">
-        <v>1.93678849</v>
+        <v>1.970181395</v>
       </c>
       <c r="N60">
-        <v>9.66321151</v>
+        <v>9.629818605000001</v>
       </c>
       <c r="O60">
-        <v>2.8023313379</v>
+        <v>2.79264739545</v>
       </c>
       <c r="P60">
-        <v>6.8608801721</v>
+        <v>6.83717120955</v>
       </c>
       <c r="Q60">
-        <v>7.4608801721</v>
+        <v>7.43717120955</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2374965750628041</v>
+        <v>0.2414874666436423</v>
       </c>
       <c r="T60">
-        <v>1.172392389789374</v>
+        <v>1.196800185892753</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.989296229243907</v>
+        <v>5.887782733832993</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1221750313238934</v>
+        <v>0.121828961121409</v>
       </c>
       <c r="C61">
-        <v>33.52824152708301</v>
+        <v>33.09587704894383</v>
       </c>
       <c r="D61">
-        <v>60.75539152708301</v>
+        <v>60.92687704894382</v>
       </c>
       <c r="E61">
-        <v>34.94215</v>
+        <v>35.546</v>
       </c>
       <c r="F61">
-        <v>35.62715</v>
+        <v>36.231</v>
       </c>
       <c r="G61">
         <v>8.4</v>
@@ -6283,28 +6283,28 @@
         <v>11.6</v>
       </c>
       <c r="M61">
-        <v>1.970181395</v>
+        <v>2.0035743</v>
       </c>
       <c r="N61">
-        <v>9.629818605000001</v>
+        <v>9.596425699999999</v>
       </c>
       <c r="O61">
-        <v>2.79264739545</v>
+        <v>2.782963453</v>
       </c>
       <c r="P61">
-        <v>6.83717120955</v>
+        <v>6.813462246999999</v>
       </c>
       <c r="Q61">
-        <v>7.43717120955</v>
+        <v>7.413462246999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2414874666436423</v>
+        <v>0.2456779028035224</v>
       </c>
       <c r="T61">
-        <v>1.196800185892753</v>
+        <v>1.222428371801302</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.887782733832993</v>
+        <v>5.789653021602442</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.121828961121409</v>
+        <v>0.1214828909189246</v>
       </c>
       <c r="C62">
-        <v>33.09587704894383</v>
+        <v>32.66448336605859</v>
       </c>
       <c r="D62">
-        <v>60.92687704894382</v>
+        <v>61.09933336605859</v>
       </c>
       <c r="E62">
-        <v>35.546</v>
+        <v>36.14985</v>
       </c>
       <c r="F62">
-        <v>36.231</v>
+        <v>36.83485</v>
       </c>
       <c r="G62">
         <v>8.4</v>
@@ -6365,28 +6365,28 @@
         <v>11.6</v>
       </c>
       <c r="M62">
-        <v>2.0035743</v>
+        <v>2.036967205</v>
       </c>
       <c r="N62">
-        <v>9.596425699999999</v>
+        <v>9.563032795</v>
       </c>
       <c r="O62">
-        <v>2.782963453</v>
+        <v>2.77327951055</v>
       </c>
       <c r="P62">
-        <v>6.813462246999999</v>
+        <v>6.789753284450001</v>
       </c>
       <c r="Q62">
-        <v>7.413462246999999</v>
+        <v>7.38975328445</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2456779028035224</v>
+        <v>0.2500832331254478</v>
       </c>
       <c r="T62">
-        <v>1.222428371801302</v>
+        <v>1.24937082365388</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>5.789653021602442</v>
+        <v>5.694740676986009</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1214828909189246</v>
+        <v>0.1211368207164403</v>
       </c>
       <c r="C63">
-        <v>32.66448336605859</v>
+        <v>32.23406874546891</v>
       </c>
       <c r="D63">
-        <v>61.09933336605859</v>
+        <v>61.27276874546892</v>
       </c>
       <c r="E63">
-        <v>36.14985</v>
+        <v>36.7537</v>
       </c>
       <c r="F63">
-        <v>36.83485</v>
+        <v>37.4387</v>
       </c>
       <c r="G63">
         <v>8.4</v>
@@ -6447,28 +6447,28 @@
         <v>11.6</v>
       </c>
       <c r="M63">
-        <v>2.036967205</v>
+        <v>2.07036011</v>
       </c>
       <c r="N63">
-        <v>9.563032795</v>
+        <v>9.529639889999999</v>
       </c>
       <c r="O63">
-        <v>2.77327951055</v>
+        <v>2.7635955681</v>
       </c>
       <c r="P63">
-        <v>6.789753284450001</v>
+        <v>6.766044321899999</v>
       </c>
       <c r="Q63">
-        <v>7.38975328445</v>
+        <v>7.366044321899999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2500832331254478</v>
+        <v>0.2547204229380007</v>
       </c>
       <c r="T63">
-        <v>1.24937082365388</v>
+        <v>1.277731299288172</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>5.694740676986009</v>
+        <v>5.602890020905589</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1211368207164403</v>
+        <v>0.1207907505139559</v>
       </c>
       <c r="C64">
-        <v>32.23406874546891</v>
+        <v>31.80464154835019</v>
       </c>
       <c r="D64">
-        <v>61.27276874546892</v>
+        <v>61.4471915483502</v>
       </c>
       <c r="E64">
-        <v>36.7537</v>
+        <v>37.35755</v>
       </c>
       <c r="F64">
-        <v>37.4387</v>
+        <v>38.04255000000001</v>
       </c>
       <c r="G64">
         <v>8.4</v>
@@ -6529,28 +6529,28 @@
         <v>11.6</v>
       </c>
       <c r="M64">
-        <v>2.07036011</v>
+        <v>2.103753015000001</v>
       </c>
       <c r="N64">
-        <v>9.529639889999999</v>
+        <v>9.496246984999999</v>
       </c>
       <c r="O64">
-        <v>2.7635955681</v>
+        <v>2.753911625649999</v>
       </c>
       <c r="P64">
-        <v>6.766044321899999</v>
+        <v>6.742335359349999</v>
       </c>
       <c r="Q64">
-        <v>7.366044321899999</v>
+        <v>7.342335359349999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2547204229380007</v>
+        <v>0.2596082716593403</v>
       </c>
       <c r="T64">
-        <v>1.277731299288172</v>
+        <v>1.307624773605399</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>5.602890020905589</v>
+        <v>5.513955258668992</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1207907505139559</v>
+        <v>0.1204446803114715</v>
       </c>
       <c r="C65">
-        <v>31.80464154835019</v>
+        <v>31.37621023135542</v>
       </c>
       <c r="D65">
-        <v>61.4471915483502</v>
+        <v>61.62261023135542</v>
       </c>
       <c r="E65">
-        <v>37.35755</v>
+        <v>37.9614</v>
       </c>
       <c r="F65">
-        <v>38.04255000000001</v>
+        <v>38.64640000000001</v>
       </c>
       <c r="G65">
         <v>8.4</v>
@@ -6611,28 +6611,28 @@
         <v>11.6</v>
       </c>
       <c r="M65">
-        <v>2.103753015000001</v>
+        <v>2.13714592</v>
       </c>
       <c r="N65">
-        <v>9.496246984999999</v>
+        <v>9.46285408</v>
       </c>
       <c r="O65">
-        <v>2.753911625649999</v>
+        <v>2.7442276832</v>
       </c>
       <c r="P65">
-        <v>6.742335359349999</v>
+        <v>6.7186263968</v>
       </c>
       <c r="Q65">
-        <v>7.342335359349999</v>
+        <v>7.318626396799999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2596082716593403</v>
+        <v>0.2647676675318654</v>
       </c>
       <c r="T65">
-        <v>1.307624773605399</v>
+        <v>1.339178996495805</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>5.513955258668992</v>
+        <v>5.427799707752289</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1204446803114715</v>
+        <v>0.1200986101089871</v>
       </c>
       <c r="C66">
-        <v>31.37621023135542</v>
+        <v>30.94878334798184</v>
       </c>
       <c r="D66">
-        <v>61.62261023135542</v>
+        <v>61.79903334798183</v>
       </c>
       <c r="E66">
-        <v>37.9614</v>
+        <v>38.56525</v>
       </c>
       <c r="F66">
-        <v>38.64640000000001</v>
+        <v>39.25025</v>
       </c>
       <c r="G66">
         <v>8.4</v>
@@ -6693,28 +6693,28 @@
         <v>11.6</v>
       </c>
       <c r="M66">
-        <v>2.13714592</v>
+        <v>2.170538825</v>
       </c>
       <c r="N66">
-        <v>9.46285408</v>
+        <v>9.429461175</v>
       </c>
       <c r="O66">
-        <v>2.7442276832</v>
+        <v>2.73454374075</v>
       </c>
       <c r="P66">
-        <v>6.7186263968</v>
+        <v>6.69491743425</v>
       </c>
       <c r="Q66">
-        <v>7.318626396799999</v>
+        <v>7.294917434249999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2647676675318654</v>
+        <v>0.2702218860256776</v>
       </c>
       <c r="T66">
-        <v>1.339178996495805</v>
+        <v>1.372536317837091</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>5.427799707752289</v>
+        <v>5.344295096863794</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1200986101089871</v>
+        <v>0.1197525399065028</v>
       </c>
       <c r="C67">
-        <v>30.94878334798184</v>
+        <v>30.52236954996117</v>
       </c>
       <c r="D67">
-        <v>61.79903334798183</v>
+        <v>61.97646954996117</v>
       </c>
       <c r="E67">
-        <v>38.56525</v>
+        <v>39.1691</v>
       </c>
       <c r="F67">
-        <v>39.25025</v>
+        <v>39.8541</v>
       </c>
       <c r="G67">
         <v>8.4</v>
@@ -6775,28 +6775,28 @@
         <v>11.6</v>
       </c>
       <c r="M67">
-        <v>2.170538825</v>
+        <v>2.20393173</v>
       </c>
       <c r="N67">
-        <v>9.429461175</v>
+        <v>9.396068269999999</v>
       </c>
       <c r="O67">
-        <v>2.73454374075</v>
+        <v>2.724859798299999</v>
       </c>
       <c r="P67">
-        <v>6.69491743425</v>
+        <v>6.6712084717</v>
       </c>
       <c r="Q67">
-        <v>7.294917434249999</v>
+        <v>7.2712084717</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2702218860256776</v>
+        <v>0.2759969409014788</v>
       </c>
       <c r="T67">
-        <v>1.372536317837091</v>
+        <v>1.407855834551394</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>5.344295096863794</v>
+        <v>5.263320928729493</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1197525399065028</v>
+        <v>0.1194064697040184</v>
       </c>
       <c r="C68">
-        <v>30.52236954996117</v>
+        <v>30.0969775886741</v>
       </c>
       <c r="D68">
-        <v>61.97646954996117</v>
+        <v>62.15492758867411</v>
       </c>
       <c r="E68">
-        <v>39.1691</v>
+        <v>39.77295</v>
       </c>
       <c r="F68">
-        <v>39.8541</v>
+        <v>40.45795</v>
       </c>
       <c r="G68">
         <v>8.4</v>
@@ -6857,28 +6857,28 @@
         <v>11.6</v>
       </c>
       <c r="M68">
-        <v>2.20393173</v>
+        <v>2.237324635</v>
       </c>
       <c r="N68">
-        <v>9.396068269999999</v>
+        <v>9.362675364999999</v>
       </c>
       <c r="O68">
-        <v>2.724859798299999</v>
+        <v>2.71517585585</v>
       </c>
       <c r="P68">
-        <v>6.6712084717</v>
+        <v>6.64749950915</v>
       </c>
       <c r="Q68">
-        <v>7.2712084717</v>
+        <v>7.24749950915</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2759969409014788</v>
+        <v>0.2821219991030862</v>
       </c>
       <c r="T68">
-        <v>1.407855834551394</v>
+        <v>1.44531592803626</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>5.263320928729493</v>
+        <v>5.184763899942486</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1194064697040184</v>
+        <v>0.1190603995015341</v>
       </c>
       <c r="C69">
-        <v>30.0969775886741</v>
+        <v>29.6726163165889</v>
       </c>
       <c r="D69">
-        <v>62.15492758867411</v>
+        <v>62.33441631658891</v>
       </c>
       <c r="E69">
-        <v>39.77295</v>
+        <v>40.3768</v>
       </c>
       <c r="F69">
-        <v>40.45795</v>
+        <v>41.06180000000001</v>
       </c>
       <c r="G69">
         <v>8.4</v>
@@ -6939,28 +6939,28 @@
         <v>11.6</v>
       </c>
       <c r="M69">
-        <v>2.237324635</v>
+        <v>2.27071754</v>
       </c>
       <c r="N69">
-        <v>9.362675364999999</v>
+        <v>9.32928246</v>
       </c>
       <c r="O69">
-        <v>2.71517585585</v>
+        <v>2.7054919134</v>
       </c>
       <c r="P69">
-        <v>6.64749950915</v>
+        <v>6.6237905466</v>
       </c>
       <c r="Q69">
-        <v>7.24749950915</v>
+        <v>7.2237905466</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2821219991030862</v>
+        <v>0.288629873442294</v>
       </c>
       <c r="T69">
-        <v>1.44531592803626</v>
+        <v>1.485117277363931</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>5.184763899942486</v>
+        <v>5.108517372002155</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1190603995015341</v>
+        <v>0.1187143292990497</v>
       </c>
       <c r="C70">
-        <v>29.6726163165889</v>
+        <v>29.24929468872538</v>
       </c>
       <c r="D70">
-        <v>62.33441631658891</v>
+        <v>62.51494468872538</v>
       </c>
       <c r="E70">
-        <v>40.3768</v>
+        <v>40.98065</v>
       </c>
       <c r="F70">
-        <v>41.06180000000001</v>
+        <v>41.66565000000001</v>
       </c>
       <c r="G70">
         <v>8.4</v>
@@ -7021,28 +7021,28 @@
         <v>11.6</v>
       </c>
       <c r="M70">
-        <v>2.27071754</v>
+        <v>2.304110445000001</v>
       </c>
       <c r="N70">
-        <v>9.32928246</v>
+        <v>9.295889554999999</v>
       </c>
       <c r="O70">
-        <v>2.7054919134</v>
+        <v>2.695807970949999</v>
       </c>
       <c r="P70">
-        <v>6.6237905466</v>
+        <v>6.600081584049999</v>
       </c>
       <c r="Q70">
-        <v>7.2237905466</v>
+        <v>7.200081584049999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.288629873442294</v>
+        <v>0.2955576106420958</v>
       </c>
       <c r="T70">
-        <v>1.485117277363931</v>
+        <v>1.527486455680485</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>5.108517372002155</v>
+        <v>5.034480888349949</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1187143292990497</v>
+        <v>0.1183682590965653</v>
       </c>
       <c r="C71">
-        <v>29.24929468872538</v>
+        <v>28.82702176414412</v>
       </c>
       <c r="D71">
-        <v>62.51494468872538</v>
+        <v>62.69652176414412</v>
       </c>
       <c r="E71">
-        <v>40.98065</v>
+        <v>41.58450000000001</v>
       </c>
       <c r="F71">
-        <v>41.66565000000001</v>
+        <v>42.26950000000001</v>
       </c>
       <c r="G71">
         <v>8.4</v>
@@ -7103,28 +7103,28 @@
         <v>11.6</v>
       </c>
       <c r="M71">
-        <v>2.304110445000001</v>
+        <v>2.33750335</v>
       </c>
       <c r="N71">
-        <v>9.295889554999999</v>
+        <v>9.262496649999999</v>
       </c>
       <c r="O71">
-        <v>2.695807970949999</v>
+        <v>2.6861240285</v>
       </c>
       <c r="P71">
-        <v>6.600081584049999</v>
+        <v>6.576372621499999</v>
       </c>
       <c r="Q71">
-        <v>7.200081584049999</v>
+        <v>7.176372621499999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2955576106420958</v>
+        <v>0.3029471969885512</v>
       </c>
       <c r="T71">
-        <v>1.527486455680485</v>
+        <v>1.572680245884808</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>5.034480888349949</v>
+        <v>4.962559732802093</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1183682590965653</v>
+        <v>0.118022188894081</v>
       </c>
       <c r="C72">
-        <v>28.82702176414412</v>
+        <v>28.40580670746184</v>
       </c>
       <c r="D72">
-        <v>62.69652176414412</v>
+        <v>62.87915670746185</v>
       </c>
       <c r="E72">
-        <v>41.58450000000001</v>
+        <v>42.18835000000001</v>
       </c>
       <c r="F72">
-        <v>42.26950000000001</v>
+        <v>42.87335000000001</v>
       </c>
       <c r="G72">
         <v>8.4</v>
@@ -7185,28 +7185,28 @@
         <v>11.6</v>
       </c>
       <c r="M72">
-        <v>2.33750335</v>
+        <v>2.370896255000001</v>
       </c>
       <c r="N72">
-        <v>9.262496649999999</v>
+        <v>9.229103745</v>
       </c>
       <c r="O72">
-        <v>2.6861240285</v>
+        <v>2.67644008605</v>
       </c>
       <c r="P72">
-        <v>6.576372621499999</v>
+        <v>6.552663658949999</v>
       </c>
       <c r="Q72">
-        <v>7.176372621499999</v>
+        <v>7.152663658949999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3029471969885512</v>
+        <v>0.3108464099795897</v>
       </c>
       <c r="T72">
-        <v>1.572680245884808</v>
+        <v>1.620990849206671</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>4.962559732802093</v>
+        <v>4.892664525297838</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.118022188894081</v>
+        <v>0.1176761186915966</v>
       </c>
       <c r="C73">
-        <v>28.40580670746185</v>
+        <v>27.98565879039344</v>
       </c>
       <c r="D73">
-        <v>62.87915670746185</v>
+        <v>63.06285879039344</v>
       </c>
       <c r="E73">
-        <v>42.18835</v>
+        <v>42.7922</v>
       </c>
       <c r="F73">
-        <v>42.87335</v>
+        <v>43.4772</v>
       </c>
       <c r="G73">
         <v>8.4</v>
@@ -7267,28 +7267,28 @@
         <v>11.6</v>
       </c>
       <c r="M73">
-        <v>2.370896255</v>
+        <v>2.40428916</v>
       </c>
       <c r="N73">
-        <v>9.229103745</v>
+        <v>9.19571084</v>
       </c>
       <c r="O73">
-        <v>2.67644008605</v>
+        <v>2.6667561436</v>
       </c>
       <c r="P73">
-        <v>6.552663658949999</v>
+        <v>6.5289546964</v>
       </c>
       <c r="Q73">
-        <v>7.152663658949999</v>
+        <v>7.1289546964</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3108464099795896</v>
+        <v>0.3193098524699879</v>
       </c>
       <c r="T73">
-        <v>1.62099084920667</v>
+        <v>1.672752209908666</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>4.892664525297839</v>
+        <v>4.824710851335369</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1176761186915966</v>
+        <v>0.1173300484891122</v>
       </c>
       <c r="C74">
-        <v>27.98565879039344</v>
+        <v>27.56658739332079</v>
       </c>
       <c r="D74">
-        <v>63.06285879039344</v>
+        <v>63.24763739332079</v>
       </c>
       <c r="E74">
-        <v>42.7922</v>
+        <v>43.39605</v>
       </c>
       <c r="F74">
-        <v>43.4772</v>
+        <v>44.08105</v>
       </c>
       <c r="G74">
         <v>8.4</v>
@@ -7349,28 +7349,28 @@
         <v>11.6</v>
       </c>
       <c r="M74">
-        <v>2.40428916</v>
+        <v>2.437682065</v>
       </c>
       <c r="N74">
-        <v>9.19571084</v>
+        <v>9.162317934999999</v>
       </c>
       <c r="O74">
-        <v>2.6667561436</v>
+        <v>2.65707220115</v>
       </c>
       <c r="P74">
-        <v>6.5289546964</v>
+        <v>6.50524573385</v>
       </c>
       <c r="Q74">
-        <v>7.1289546964</v>
+        <v>7.105245733849999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3193098524699879</v>
+        <v>0.3284002166263416</v>
       </c>
       <c r="T74">
-        <v>1.672752209908666</v>
+        <v>1.728347745477476</v>
       </c>
       <c r="U74">
         <v>0.0553</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>4.824710851335369</v>
+        <v>4.758618921865021</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1173300484891122</v>
+        <v>0.1169839782866279</v>
       </c>
       <c r="C75">
-        <v>27.56658739332079</v>
+        <v>27.14860200688961</v>
       </c>
       <c r="D75">
-        <v>63.24763739332079</v>
+        <v>63.43350200688961</v>
       </c>
       <c r="E75">
-        <v>43.39605</v>
+        <v>43.9999</v>
       </c>
       <c r="F75">
-        <v>44.08105</v>
+        <v>44.68490000000001</v>
       </c>
       <c r="G75">
         <v>8.4</v>
@@ -7431,28 +7431,28 @@
         <v>11.6</v>
       </c>
       <c r="M75">
-        <v>2.437682065</v>
+        <v>2.471074970000001</v>
       </c>
       <c r="N75">
-        <v>9.162317934999999</v>
+        <v>9.12892503</v>
       </c>
       <c r="O75">
-        <v>2.65707220115</v>
+        <v>2.647388258699999</v>
       </c>
       <c r="P75">
-        <v>6.50524573385</v>
+        <v>6.4815367713</v>
       </c>
       <c r="Q75">
-        <v>7.105245733849999</v>
+        <v>7.0815367713</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3284002166263416</v>
+        <v>0.3381898395639533</v>
       </c>
       <c r="T75">
-        <v>1.728347745477476</v>
+        <v>1.788219860705426</v>
       </c>
       <c r="U75">
         <v>0.0553</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>4.758618921865021</v>
+        <v>4.694313260758737</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1169839782866279</v>
+        <v>0.1166379080841435</v>
       </c>
       <c r="C76">
-        <v>27.14860200688961</v>
+        <v>26.73171223363435</v>
       </c>
       <c r="D76">
-        <v>63.43350200688961</v>
+        <v>63.62046223363436</v>
       </c>
       <c r="E76">
-        <v>43.9999</v>
+        <v>44.60375000000001</v>
       </c>
       <c r="F76">
-        <v>44.68490000000001</v>
+        <v>45.28875000000001</v>
       </c>
       <c r="G76">
         <v>8.4</v>
@@ -7513,28 +7513,28 @@
         <v>11.6</v>
       </c>
       <c r="M76">
-        <v>2.471074970000001</v>
+        <v>2.504467875</v>
       </c>
       <c r="N76">
-        <v>9.12892503</v>
+        <v>9.095532124999998</v>
       </c>
       <c r="O76">
-        <v>2.647388258699999</v>
+        <v>2.637704316249999</v>
       </c>
       <c r="P76">
-        <v>6.4815367713</v>
+        <v>6.457827808749999</v>
       </c>
       <c r="Q76">
-        <v>7.0815367713</v>
+        <v>7.057827808749998</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3381898395639533</v>
+        <v>0.3487626323365741</v>
       </c>
       <c r="T76">
-        <v>1.788219860705426</v>
+        <v>1.852881745151612</v>
       </c>
       <c r="U76">
         <v>0.0553</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>4.694313260758737</v>
+        <v>4.631722417281953</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1166379080841435</v>
+        <v>0.1162918378816591</v>
       </c>
       <c r="C77">
-        <v>26.73171223363435</v>
+        <v>26.31592778963191</v>
       </c>
       <c r="D77">
-        <v>63.62046223363436</v>
+        <v>63.80852778963192</v>
       </c>
       <c r="E77">
-        <v>44.60375000000001</v>
+        <v>45.2076</v>
       </c>
       <c r="F77">
-        <v>45.28875000000001</v>
+        <v>45.8926</v>
       </c>
       <c r="G77">
         <v>8.4</v>
@@ -7595,28 +7595,28 @@
         <v>11.6</v>
       </c>
       <c r="M77">
-        <v>2.504467875</v>
+        <v>2.53786078</v>
       </c>
       <c r="N77">
-        <v>9.095532124999998</v>
+        <v>9.062139219999999</v>
       </c>
       <c r="O77">
-        <v>2.637704316249999</v>
+        <v>2.6280203738</v>
       </c>
       <c r="P77">
-        <v>6.457827808749999</v>
+        <v>6.434118846199999</v>
       </c>
       <c r="Q77">
-        <v>7.057827808749998</v>
+        <v>7.034118846199998</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3487626323365741</v>
+        <v>0.3602164911735798</v>
       </c>
       <c r="T77">
-        <v>1.852881745151612</v>
+        <v>1.922932119968313</v>
       </c>
       <c r="U77">
         <v>0.0553</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>4.631722417281953</v>
+        <v>4.570778701265086</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1162918378816591</v>
+        <v>0.1159457676791748</v>
       </c>
       <c r="C78">
-        <v>26.31592778963191</v>
+        <v>25.9012585061848</v>
       </c>
       <c r="D78">
-        <v>63.80852778963192</v>
+        <v>63.9977085061848</v>
       </c>
       <c r="E78">
-        <v>45.2076</v>
+        <v>45.81145</v>
       </c>
       <c r="F78">
-        <v>45.8926</v>
+        <v>46.49645</v>
       </c>
       <c r="G78">
         <v>8.4</v>
@@ -7677,28 +7677,28 @@
         <v>11.6</v>
       </c>
       <c r="M78">
-        <v>2.53786078</v>
+        <v>2.571253685</v>
       </c>
       <c r="N78">
-        <v>9.062139219999999</v>
+        <v>9.028746314999999</v>
       </c>
       <c r="O78">
-        <v>2.6280203738</v>
+        <v>2.618336431349999</v>
       </c>
       <c r="P78">
-        <v>6.434118846199999</v>
+        <v>6.41040988365</v>
       </c>
       <c r="Q78">
-        <v>7.034118846199998</v>
+        <v>7.01040988365</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3602164911735798</v>
+        <v>0.3726663377355425</v>
       </c>
       <c r="T78">
-        <v>1.922932119968313</v>
+        <v>1.999073831725596</v>
       </c>
       <c r="U78">
         <v>0.0553</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>4.570778701265086</v>
+        <v>4.511417938910994</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1159457676791748</v>
+        <v>0.1169841974766904</v>
       </c>
       <c r="C79">
-        <v>25.9012585061848</v>
+        <v>24.73308394032152</v>
       </c>
       <c r="D79">
-        <v>63.9977085061848</v>
+        <v>63.43338394032152</v>
       </c>
       <c r="E79">
-        <v>45.81145</v>
+        <v>46.4153</v>
       </c>
       <c r="F79">
-        <v>46.49645</v>
+        <v>47.1003</v>
       </c>
       <c r="G79">
         <v>8.4</v>
@@ -7759,45 +7759,45 @@
         <v>11.6</v>
       </c>
       <c r="M79">
-        <v>2.571253685</v>
+        <v>2.722397340000001</v>
       </c>
       <c r="N79">
-        <v>9.028746314999999</v>
+        <v>8.877602659999999</v>
       </c>
       <c r="O79">
-        <v>2.618336431349999</v>
+        <v>2.5745047714</v>
       </c>
       <c r="P79">
-        <v>6.41040988365</v>
+        <v>6.3030978886</v>
       </c>
       <c r="Q79">
-        <v>7.01040988365</v>
+        <v>6.9030978886</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3726663377355425</v>
+        <v>0.386247988530411</v>
       </c>
       <c r="T79">
-        <v>1.999073831725596</v>
+        <v>2.082137517278997</v>
       </c>
       <c r="U79">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V79">
         <v>0.29</v>
       </c>
       <c r="W79">
-        <v>0.039263</v>
+        <v>0.041038</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y79">
-        <v>4.511417938910994</v>
+        <v>4.260950387205417</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1169841974766904</v>
+        <v>0.116655877274206</v>
       </c>
       <c r="C80">
-        <v>24.73308394032152</v>
+        <v>24.30657747483624</v>
       </c>
       <c r="D80">
-        <v>63.43338394032152</v>
+        <v>63.61072747483624</v>
       </c>
       <c r="E80">
-        <v>46.4153</v>
+        <v>47.01915</v>
       </c>
       <c r="F80">
-        <v>47.1003</v>
+        <v>47.70415000000001</v>
       </c>
       <c r="G80">
         <v>8.4</v>
@@ -7841,28 +7841,28 @@
         <v>11.6</v>
       </c>
       <c r="M80">
-        <v>2.722397340000001</v>
+        <v>2.757299870000001</v>
       </c>
       <c r="N80">
-        <v>8.877602659999999</v>
+        <v>8.842700129999999</v>
       </c>
       <c r="O80">
-        <v>2.5745047714</v>
+        <v>2.564383037699999</v>
       </c>
       <c r="P80">
-        <v>6.3030978886</v>
+        <v>6.2783170923</v>
       </c>
       <c r="Q80">
-        <v>6.9030978886</v>
+        <v>6.8783170923</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.386247988530411</v>
+        <v>0.4011231298771717</v>
       </c>
       <c r="T80">
-        <v>2.082137517278997</v>
+        <v>2.173112030027959</v>
       </c>
       <c r="U80">
         <v>0.0578</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>4.260950387205417</v>
+        <v>4.207014306354715</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.116655877274206</v>
+        <v>0.1163275570717217</v>
       </c>
       <c r="C81">
-        <v>24.30657747483624</v>
+        <v>23.88106540384774</v>
       </c>
       <c r="D81">
-        <v>63.61072747483624</v>
+        <v>63.78906540384774</v>
       </c>
       <c r="E81">
-        <v>47.01915</v>
+        <v>47.623</v>
       </c>
       <c r="F81">
-        <v>47.70415000000001</v>
+        <v>48.30800000000001</v>
       </c>
       <c r="G81">
         <v>8.4</v>
@@ -7923,28 +7923,28 @@
         <v>11.6</v>
       </c>
       <c r="M81">
-        <v>2.757299870000001</v>
+        <v>2.792202400000001</v>
       </c>
       <c r="N81">
-        <v>8.842700129999999</v>
+        <v>8.807797599999999</v>
       </c>
       <c r="O81">
-        <v>2.564383037699999</v>
+        <v>2.554261303999999</v>
       </c>
       <c r="P81">
-        <v>6.2783170923</v>
+        <v>6.253536296</v>
       </c>
       <c r="Q81">
-        <v>6.8783170923</v>
+        <v>6.853536296</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4011231298771717</v>
+        <v>0.4174857853586085</v>
       </c>
       <c r="T81">
-        <v>2.173112030027959</v>
+        <v>2.273183994051818</v>
       </c>
       <c r="U81">
         <v>0.0578</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>4.207014306354715</v>
+        <v>4.154426627525281</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1163275570717217</v>
+        <v>0.1159992368692373</v>
       </c>
       <c r="C82">
-        <v>23.88106540384774</v>
+        <v>23.45655611447135</v>
       </c>
       <c r="D82">
-        <v>63.78906540384774</v>
+        <v>63.96840611447135</v>
       </c>
       <c r="E82">
-        <v>47.623</v>
+        <v>48.22685000000001</v>
       </c>
       <c r="F82">
-        <v>48.30800000000001</v>
+        <v>48.91185000000001</v>
       </c>
       <c r="G82">
         <v>8.4</v>
@@ -8005,28 +8005,28 @@
         <v>11.6</v>
       </c>
       <c r="M82">
-        <v>2.792202400000001</v>
+        <v>2.827104930000001</v>
       </c>
       <c r="N82">
-        <v>8.807797599999999</v>
+        <v>8.772895069999999</v>
       </c>
       <c r="O82">
-        <v>2.554261303999999</v>
+        <v>2.5441395703</v>
       </c>
       <c r="P82">
-        <v>6.253536296</v>
+        <v>6.228755499699999</v>
       </c>
       <c r="Q82">
-        <v>6.853536296</v>
+        <v>6.828755499699999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4174857853586085</v>
+        <v>0.4355708256275649</v>
       </c>
       <c r="T82">
-        <v>2.273183994051818</v>
+        <v>2.383789849025556</v>
       </c>
       <c r="U82">
         <v>0.0578</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>4.154426627525281</v>
+        <v>4.103137409901512</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1159992368692373</v>
+        <v>0.1156709166667529</v>
       </c>
       <c r="C83">
-        <v>23.45655611447135</v>
+        <v>23.03305808840861</v>
       </c>
       <c r="D83">
-        <v>63.96840611447135</v>
+        <v>64.14875808840861</v>
       </c>
       <c r="E83">
-        <v>48.22685000000001</v>
+        <v>48.83070000000001</v>
       </c>
       <c r="F83">
-        <v>48.91185000000001</v>
+        <v>49.51570000000001</v>
       </c>
       <c r="G83">
         <v>8.4</v>
@@ -8087,28 +8087,28 @@
         <v>11.6</v>
       </c>
       <c r="M83">
-        <v>2.827104930000001</v>
+        <v>2.862007460000001</v>
       </c>
       <c r="N83">
-        <v>8.772895069999999</v>
+        <v>8.737992539999999</v>
       </c>
       <c r="O83">
-        <v>2.5441395703</v>
+        <v>2.534017836599999</v>
       </c>
       <c r="P83">
-        <v>6.228755499699999</v>
+        <v>6.203974703399999</v>
       </c>
       <c r="Q83">
-        <v>6.828755499699999</v>
+        <v>6.803974703399999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4355708256275649</v>
+        <v>0.4556653148152943</v>
       </c>
       <c r="T83">
-        <v>2.383789849025556</v>
+        <v>2.506685243440821</v>
       </c>
       <c r="U83">
         <v>0.0578</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>4.103137409901512</v>
+        <v>4.053099148805153</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1156709166667529</v>
+        <v>0.1153425964642686</v>
       </c>
       <c r="C84">
-        <v>23.03305808840861</v>
+        <v>22.61057990328447</v>
       </c>
       <c r="D84">
-        <v>64.14875808840861</v>
+        <v>64.33012990328447</v>
       </c>
       <c r="E84">
-        <v>48.83070000000001</v>
+        <v>49.43455000000001</v>
       </c>
       <c r="F84">
-        <v>49.51570000000001</v>
+        <v>50.11955000000001</v>
       </c>
       <c r="G84">
         <v>8.4</v>
@@ -8169,28 +8169,28 @@
         <v>11.6</v>
       </c>
       <c r="M84">
-        <v>2.862007460000001</v>
+        <v>2.896909990000001</v>
       </c>
       <c r="N84">
-        <v>8.737992539999999</v>
+        <v>8.703090009999999</v>
       </c>
       <c r="O84">
-        <v>2.534017836599999</v>
+        <v>2.523896102899999</v>
       </c>
       <c r="P84">
-        <v>6.203974703399999</v>
+        <v>6.179193907099999</v>
       </c>
       <c r="Q84">
-        <v>6.803974703399999</v>
+        <v>6.779193907099999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4556653148152943</v>
+        <v>0.4781238615545212</v>
       </c>
       <c r="T84">
-        <v>2.506685243440821</v>
+        <v>2.644038919552</v>
       </c>
       <c r="U84">
         <v>0.0578</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>4.053099148805153</v>
+        <v>4.00426662894003</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1153425964642686</v>
+        <v>0.1171016762617842</v>
       </c>
       <c r="C85">
-        <v>22.61057990328447</v>
+        <v>21.04676725935143</v>
       </c>
       <c r="D85">
-        <v>64.33012990328447</v>
+        <v>63.37016725935144</v>
       </c>
       <c r="E85">
-        <v>49.43455000000001</v>
+        <v>50.03840000000001</v>
       </c>
       <c r="F85">
-        <v>50.11955000000001</v>
+        <v>50.72340000000001</v>
       </c>
       <c r="G85">
         <v>8.4</v>
@@ -8251,45 +8251,45 @@
         <v>11.6</v>
       </c>
       <c r="M85">
-        <v>2.896909990000001</v>
+        <v>3.109344420000001</v>
       </c>
       <c r="N85">
-        <v>8.703090009999999</v>
+        <v>8.490655579999999</v>
       </c>
       <c r="O85">
-        <v>2.523896102899999</v>
+        <v>2.462290118199999</v>
       </c>
       <c r="P85">
-        <v>6.179193907099999</v>
+        <v>6.028365461799999</v>
       </c>
       <c r="Q85">
-        <v>6.779193907099999</v>
+        <v>6.628365461799999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4781238615545212</v>
+        <v>0.5033897266361517</v>
       </c>
       <c r="T85">
-        <v>2.644038919552</v>
+        <v>2.798561805177076</v>
       </c>
       <c r="U85">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V85">
         <v>0.29</v>
       </c>
       <c r="W85">
-        <v>0.041038</v>
+        <v>0.043523</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y85">
-        <v>4.00426662894003</v>
+        <v>3.730689956823759</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1171016762617842</v>
+        <v>0.1167982060592998</v>
       </c>
       <c r="C86">
-        <v>21.04676725935145</v>
+        <v>20.6064763723421</v>
       </c>
       <c r="D86">
-        <v>63.37016725935145</v>
+        <v>63.5337263723421</v>
       </c>
       <c r="E86">
-        <v>50.0384</v>
+        <v>50.64225</v>
       </c>
       <c r="F86">
-        <v>50.72340000000001</v>
+        <v>51.32725000000001</v>
       </c>
       <c r="G86">
         <v>8.4</v>
@@ -8333,28 +8333,28 @@
         <v>11.6</v>
       </c>
       <c r="M86">
-        <v>3.10934442</v>
+        <v>3.146360425000001</v>
       </c>
       <c r="N86">
-        <v>8.490655579999999</v>
+        <v>8.453639574999999</v>
       </c>
       <c r="O86">
-        <v>2.462290118199999</v>
+        <v>2.451555476749999</v>
       </c>
       <c r="P86">
-        <v>6.028365461799999</v>
+        <v>6.002084098249999</v>
       </c>
       <c r="Q86">
-        <v>6.628365461799999</v>
+        <v>6.602084098249999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.5033897266361513</v>
+        <v>0.5320243737286655</v>
       </c>
       <c r="T86">
-        <v>2.798561805177074</v>
+        <v>2.973687742218826</v>
       </c>
       <c r="U86">
         <v>0.0613</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>3.73068995682376</v>
+        <v>3.68679948674348</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1167982060592998</v>
+        <v>0.1164947358568155</v>
       </c>
       <c r="C87">
-        <v>20.6064763723421</v>
+        <v>20.16703196592162</v>
       </c>
       <c r="D87">
-        <v>63.5337263723421</v>
+        <v>63.69813196592162</v>
       </c>
       <c r="E87">
-        <v>50.64225</v>
+        <v>51.2461</v>
       </c>
       <c r="F87">
-        <v>51.32725000000001</v>
+        <v>51.9311</v>
       </c>
       <c r="G87">
         <v>8.4</v>
@@ -8415,28 +8415,28 @@
         <v>11.6</v>
       </c>
       <c r="M87">
-        <v>3.146360425000001</v>
+        <v>3.18337643</v>
       </c>
       <c r="N87">
-        <v>8.453639574999999</v>
+        <v>8.416623569999999</v>
       </c>
       <c r="O87">
-        <v>2.451555476749999</v>
+        <v>2.440820835299999</v>
       </c>
       <c r="P87">
-        <v>6.002084098249999</v>
+        <v>5.975802734699999</v>
       </c>
       <c r="Q87">
-        <v>6.602084098249999</v>
+        <v>6.575802734699999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5320243737286655</v>
+        <v>0.5647496846915391</v>
       </c>
       <c r="T87">
-        <v>2.973687742218826</v>
+        <v>3.173831670266544</v>
       </c>
       <c r="U87">
         <v>0.0613</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.68679948674348</v>
+        <v>3.643929725269719</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1164947358568155</v>
+        <v>0.1161912656543311</v>
       </c>
       <c r="C88">
-        <v>20.16703196592162</v>
+        <v>19.72844062842686</v>
       </c>
       <c r="D88">
-        <v>63.69813196592162</v>
+        <v>63.86339062842686</v>
       </c>
       <c r="E88">
-        <v>51.2461</v>
+        <v>51.84995</v>
       </c>
       <c r="F88">
-        <v>51.9311</v>
+        <v>52.53495</v>
       </c>
       <c r="G88">
         <v>8.4</v>
@@ -8497,28 +8497,28 @@
         <v>11.6</v>
       </c>
       <c r="M88">
-        <v>3.18337643</v>
+        <v>3.220392435</v>
       </c>
       <c r="N88">
-        <v>8.416623569999999</v>
+        <v>8.379607565000001</v>
       </c>
       <c r="O88">
-        <v>2.440820835299999</v>
+        <v>2.43008619385</v>
       </c>
       <c r="P88">
-        <v>5.975802734699999</v>
+        <v>5.94952137115</v>
       </c>
       <c r="Q88">
-        <v>6.575802734699999</v>
+        <v>6.54952137115</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5647496846915391</v>
+        <v>0.6025096588794701</v>
       </c>
       <c r="T88">
-        <v>3.173831670266544</v>
+        <v>3.404766971860063</v>
       </c>
       <c r="U88">
         <v>0.0613</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>3.643929725269719</v>
+        <v>3.602045475553976</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1161912656543311</v>
+        <v>0.1158877954518468</v>
       </c>
       <c r="C89">
-        <v>19.72844062842686</v>
+        <v>19.29070901674372</v>
       </c>
       <c r="D89">
-        <v>63.86339062842686</v>
+        <v>64.02950901674372</v>
       </c>
       <c r="E89">
-        <v>51.84995</v>
+        <v>52.4538</v>
       </c>
       <c r="F89">
-        <v>52.53495</v>
+        <v>53.1388</v>
       </c>
       <c r="G89">
         <v>8.4</v>
@@ -8579,28 +8579,28 @@
         <v>11.6</v>
       </c>
       <c r="M89">
-        <v>3.220392435</v>
+        <v>3.25740844</v>
       </c>
       <c r="N89">
-        <v>8.379607565000001</v>
+        <v>8.342591559999999</v>
       </c>
       <c r="O89">
-        <v>2.43008619385</v>
+        <v>2.419351552399999</v>
       </c>
       <c r="P89">
-        <v>5.94952137115</v>
+        <v>5.9232400076</v>
       </c>
       <c r="Q89">
-        <v>6.54952137115</v>
+        <v>6.523240007599999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.6025096588794701</v>
+        <v>0.646562962098723</v>
       </c>
       <c r="T89">
-        <v>3.404766971860063</v>
+        <v>3.674191490385837</v>
       </c>
       <c r="U89">
         <v>0.0613</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>3.602045475553976</v>
+        <v>3.561113140604498</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1158877954518468</v>
+        <v>0.1155843252493624</v>
       </c>
       <c r="C90">
-        <v>19.29070901674372</v>
+        <v>18.85384385720106</v>
       </c>
       <c r="D90">
-        <v>64.02950901674372</v>
+        <v>64.19649385720106</v>
       </c>
       <c r="E90">
-        <v>52.4538</v>
+        <v>53.05765</v>
       </c>
       <c r="F90">
-        <v>53.1388</v>
+        <v>53.74265</v>
       </c>
       <c r="G90">
         <v>8.4</v>
@@ -8661,28 +8661,28 @@
         <v>11.6</v>
       </c>
       <c r="M90">
-        <v>3.25740844</v>
+        <v>3.294424445</v>
       </c>
       <c r="N90">
-        <v>8.342591559999999</v>
+        <v>8.305575554999999</v>
       </c>
       <c r="O90">
-        <v>2.419351552399999</v>
+        <v>2.40861691095</v>
       </c>
       <c r="P90">
-        <v>5.9232400076</v>
+        <v>5.896958644049999</v>
       </c>
       <c r="Q90">
-        <v>6.523240007599999</v>
+        <v>6.496958644049998</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.646562962098723</v>
+        <v>0.6986259568123854</v>
       </c>
       <c r="T90">
-        <v>3.674191490385837</v>
+        <v>3.992602285007205</v>
       </c>
       <c r="U90">
         <v>0.0613</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>3.561113140604498</v>
+        <v>3.521100633406695</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1155843252493624</v>
+        <v>0.117070055046878</v>
       </c>
       <c r="C91">
-        <v>18.85384385720106</v>
+        <v>17.44067060104668</v>
       </c>
       <c r="D91">
-        <v>64.19649385720106</v>
+        <v>63.38717060104668</v>
       </c>
       <c r="E91">
-        <v>53.05765</v>
+        <v>53.6615</v>
       </c>
       <c r="F91">
-        <v>53.74265</v>
+        <v>54.34650000000001</v>
       </c>
       <c r="G91">
         <v>8.4</v>
@@ -8743,45 +8743,45 @@
         <v>11.6</v>
       </c>
       <c r="M91">
-        <v>3.294424445</v>
+        <v>3.483610650000001</v>
       </c>
       <c r="N91">
-        <v>8.305575554999999</v>
+        <v>8.116389349999999</v>
       </c>
       <c r="O91">
-        <v>2.40861691095</v>
+        <v>2.3537529115</v>
       </c>
       <c r="P91">
-        <v>5.896958644049999</v>
+        <v>5.7626364385</v>
       </c>
       <c r="Q91">
-        <v>6.496958644049998</v>
+        <v>6.362636438499999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6986259568123854</v>
+        <v>0.7611015504687803</v>
       </c>
       <c r="T91">
-        <v>3.992602285007205</v>
+        <v>4.374695238552847</v>
       </c>
       <c r="U91">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V91">
         <v>0.29</v>
       </c>
       <c r="W91">
-        <v>0.043523</v>
+        <v>0.045511</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y91">
-        <v>3.521100633406695</v>
+        <v>3.329878440921633</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.117070055046878</v>
+        <v>0.1167864648443937</v>
       </c>
       <c r="C92">
-        <v>17.44067060104668</v>
+        <v>16.98972141541557</v>
       </c>
       <c r="D92">
-        <v>63.38717060104668</v>
+        <v>63.54007141541558</v>
       </c>
       <c r="E92">
-        <v>53.6615</v>
+        <v>54.26535000000001</v>
       </c>
       <c r="F92">
-        <v>54.34650000000001</v>
+        <v>54.95035000000001</v>
       </c>
       <c r="G92">
         <v>8.4</v>
@@ -8825,28 +8825,28 @@
         <v>11.6</v>
       </c>
       <c r="M92">
-        <v>3.483610650000001</v>
+        <v>3.522317435000001</v>
       </c>
       <c r="N92">
-        <v>8.116389349999999</v>
+        <v>8.077682565</v>
       </c>
       <c r="O92">
-        <v>2.3537529115</v>
+        <v>2.34252794385</v>
       </c>
       <c r="P92">
-        <v>5.7626364385</v>
+        <v>5.73515462115</v>
       </c>
       <c r="Q92">
-        <v>6.362636438499999</v>
+        <v>6.33515462115</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.7611015504687803</v>
+        <v>0.8374606093821521</v>
       </c>
       <c r="T92">
-        <v>4.374695238552847</v>
+        <v>4.841697737330855</v>
       </c>
       <c r="U92">
         <v>0.0641</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>3.329878440921633</v>
+        <v>3.293286370142275</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1167864648443937</v>
+        <v>0.1165028746419093</v>
       </c>
       <c r="C93">
-        <v>16.98972141541557</v>
+        <v>16.53951165981552</v>
       </c>
       <c r="D93">
-        <v>63.54007141541558</v>
+        <v>63.69371165981552</v>
       </c>
       <c r="E93">
-        <v>54.26535000000001</v>
+        <v>54.86920000000001</v>
       </c>
       <c r="F93">
-        <v>54.95035000000001</v>
+        <v>55.55420000000001</v>
       </c>
       <c r="G93">
         <v>8.4</v>
@@ -8907,28 +8907,28 @@
         <v>11.6</v>
       </c>
       <c r="M93">
-        <v>3.522317435000001</v>
+        <v>3.561024220000001</v>
       </c>
       <c r="N93">
-        <v>8.077682565</v>
+        <v>8.038975779999999</v>
       </c>
       <c r="O93">
-        <v>2.34252794385</v>
+        <v>2.331302976199999</v>
       </c>
       <c r="P93">
-        <v>5.73515462115</v>
+        <v>5.7076728038</v>
       </c>
       <c r="Q93">
-        <v>6.33515462115</v>
+        <v>6.307672803799999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.8374606093821521</v>
+        <v>0.9329094330238665</v>
       </c>
       <c r="T93">
-        <v>4.841697737330855</v>
+        <v>5.425450860803363</v>
       </c>
       <c r="U93">
         <v>0.0641</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>3.293286370142275</v>
+        <v>3.257489779162468</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1165028746419093</v>
+        <v>0.1162192844394249</v>
       </c>
       <c r="C94">
-        <v>16.53951165981552</v>
+        <v>16.09004671108539</v>
       </c>
       <c r="D94">
-        <v>63.69371165981552</v>
+        <v>63.8480967110854</v>
       </c>
       <c r="E94">
-        <v>54.86920000000001</v>
+        <v>55.47305000000001</v>
       </c>
       <c r="F94">
-        <v>55.55420000000001</v>
+        <v>56.15805000000001</v>
       </c>
       <c r="G94">
         <v>8.4</v>
@@ -8989,28 +8989,28 @@
         <v>11.6</v>
       </c>
       <c r="M94">
-        <v>3.561024220000001</v>
+        <v>3.599731005000001</v>
       </c>
       <c r="N94">
-        <v>8.038975779999999</v>
+        <v>8.000268994999999</v>
       </c>
       <c r="O94">
-        <v>2.331302976199999</v>
+        <v>2.320078008549999</v>
       </c>
       <c r="P94">
-        <v>5.7076728038</v>
+        <v>5.68019098645</v>
       </c>
       <c r="Q94">
-        <v>6.307672803799999</v>
+        <v>6.280190986449999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.9329094330238665</v>
+        <v>1.055629349134642</v>
       </c>
       <c r="T94">
-        <v>5.425450860803363</v>
+        <v>6.175990590982304</v>
       </c>
       <c r="U94">
         <v>0.0641</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>3.257489779162468</v>
+        <v>3.222463007343516</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1162192844394249</v>
+        <v>0.1159356942369406</v>
       </c>
       <c r="C95">
-        <v>16.09004671108539</v>
+        <v>15.64133199832182</v>
       </c>
       <c r="D95">
-        <v>63.8480967110854</v>
+        <v>64.00323199832182</v>
       </c>
       <c r="E95">
-        <v>55.47305000000001</v>
+        <v>56.07690000000001</v>
       </c>
       <c r="F95">
-        <v>56.15805000000001</v>
+        <v>56.76190000000001</v>
       </c>
       <c r="G95">
         <v>8.4</v>
@@ -9071,28 +9071,28 @@
         <v>11.6</v>
       </c>
       <c r="M95">
-        <v>3.599731005000001</v>
+        <v>3.638437790000001</v>
       </c>
       <c r="N95">
-        <v>8.000268994999999</v>
+        <v>7.961562209999999</v>
       </c>
       <c r="O95">
-        <v>2.320078008549999</v>
+        <v>2.308853040899999</v>
       </c>
       <c r="P95">
-        <v>5.68019098645</v>
+        <v>5.6527091691</v>
       </c>
       <c r="Q95">
-        <v>6.280190986449999</v>
+        <v>6.252709169099999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.055629349134642</v>
+        <v>1.219255903949011</v>
       </c>
       <c r="T95">
-        <v>6.175990590982304</v>
+        <v>7.176710231220891</v>
       </c>
       <c r="U95">
         <v>0.0641</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>3.222463007343516</v>
+        <v>3.188181485988797</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1159356942369406</v>
+        <v>0.1156521040344562</v>
       </c>
       <c r="C96">
-        <v>15.64133199832182</v>
+        <v>15.19337300351538</v>
       </c>
       <c r="D96">
-        <v>64.00323199832182</v>
+        <v>64.15912300351538</v>
       </c>
       <c r="E96">
-        <v>56.07690000000001</v>
+        <v>56.68075</v>
       </c>
       <c r="F96">
-        <v>56.76190000000001</v>
+        <v>57.36575000000001</v>
       </c>
       <c r="G96">
         <v>8.4</v>
@@ -9153,28 +9153,28 @@
         <v>11.6</v>
       </c>
       <c r="M96">
-        <v>3.638437790000001</v>
+        <v>3.677144575000001</v>
       </c>
       <c r="N96">
-        <v>7.961562209999999</v>
+        <v>7.922855424999999</v>
       </c>
       <c r="O96">
-        <v>2.308853040899999</v>
+        <v>2.297628073249999</v>
       </c>
       <c r="P96">
-        <v>5.6527091691</v>
+        <v>5.62522735175</v>
       </c>
       <c r="Q96">
-        <v>6.252709169099999</v>
+        <v>6.225227351749999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.219255903949011</v>
+        <v>1.448333080689126</v>
       </c>
       <c r="T96">
-        <v>7.176710231220891</v>
+        <v>8.577717727554916</v>
       </c>
       <c r="U96">
         <v>0.0641</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>3.188181485988797</v>
+        <v>3.154621680873126</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1156521040344562</v>
+        <v>0.1153685138319718</v>
       </c>
       <c r="C97">
-        <v>15.19337300351538</v>
+        <v>14.74617526219649</v>
       </c>
       <c r="D97">
-        <v>64.15912300351538</v>
+        <v>64.3157752621965</v>
       </c>
       <c r="E97">
-        <v>56.68075</v>
+        <v>57.2846</v>
       </c>
       <c r="F97">
-        <v>57.36575000000001</v>
+        <v>57.96960000000001</v>
       </c>
       <c r="G97">
         <v>8.4</v>
@@ -9235,28 +9235,28 @@
         <v>11.6</v>
       </c>
       <c r="M97">
-        <v>3.677144575000001</v>
+        <v>3.715851360000001</v>
       </c>
       <c r="N97">
-        <v>7.922855424999999</v>
+        <v>7.884148639999999</v>
       </c>
       <c r="O97">
-        <v>2.297628073249999</v>
+        <v>2.2864031056</v>
       </c>
       <c r="P97">
-        <v>5.62522735175</v>
+        <v>5.5977455344</v>
       </c>
       <c r="Q97">
-        <v>6.225227351749999</v>
+        <v>6.197745534399999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.448333080689126</v>
+        <v>1.791948845799299</v>
       </c>
       <c r="T97">
-        <v>8.577717727554916</v>
+        <v>10.67922897205595</v>
       </c>
       <c r="U97">
         <v>0.0641</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>3.154621680873126</v>
+        <v>3.121761038364031</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1153685138319718</v>
+        <v>0.1150849236294875</v>
       </c>
       <c r="C98">
-        <v>14.7461752621965</v>
+        <v>14.29974436409049</v>
       </c>
       <c r="D98">
-        <v>64.3157752621965</v>
+        <v>64.47319436409049</v>
       </c>
       <c r="E98">
-        <v>57.2846</v>
+        <v>57.88845</v>
       </c>
       <c r="F98">
-        <v>57.9696</v>
+        <v>58.57345</v>
       </c>
       <c r="G98">
         <v>8.4</v>
@@ -9317,28 +9317,28 @@
         <v>11.6</v>
       </c>
       <c r="M98">
-        <v>3.71585136</v>
+        <v>3.754558145</v>
       </c>
       <c r="N98">
-        <v>7.884148639999999</v>
+        <v>7.845441854999999</v>
       </c>
       <c r="O98">
-        <v>2.2864031056</v>
+        <v>2.275178137949999</v>
       </c>
       <c r="P98">
-        <v>5.5977455344</v>
+        <v>5.57026371705</v>
       </c>
       <c r="Q98">
-        <v>6.197745534399999</v>
+        <v>6.170263717049999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.791948845799294</v>
+        <v>2.36464178764958</v>
       </c>
       <c r="T98">
-        <v>10.67922897205592</v>
+        <v>14.18174771289097</v>
       </c>
       <c r="U98">
         <v>0.0641</v>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>3.121761038364032</v>
+        <v>3.089577934875742</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1150849236294875</v>
+        <v>0.1148013334270031</v>
       </c>
       <c r="C99">
-        <v>14.29974436409049</v>
+        <v>13.85408595378263</v>
       </c>
       <c r="D99">
-        <v>64.47319436409049</v>
+        <v>64.63138595378263</v>
       </c>
       <c r="E99">
-        <v>57.88845</v>
+        <v>58.4923</v>
       </c>
       <c r="F99">
-        <v>58.57345</v>
+        <v>59.1773</v>
       </c>
       <c r="G99">
         <v>8.4</v>
@@ -9399,28 +9399,28 @@
         <v>11.6</v>
       </c>
       <c r="M99">
-        <v>3.754558145</v>
+        <v>3.79326493</v>
       </c>
       <c r="N99">
-        <v>7.845441854999999</v>
+        <v>7.806735069999999</v>
       </c>
       <c r="O99">
-        <v>2.275178137949999</v>
+        <v>2.2639531703</v>
       </c>
       <c r="P99">
-        <v>5.57026371705</v>
+        <v>5.5427818997</v>
       </c>
       <c r="Q99">
-        <v>6.170263717049999</v>
+        <v>6.142781899699999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.36464178764958</v>
+        <v>3.510027671350152</v>
       </c>
       <c r="T99">
-        <v>14.18174771289097</v>
+        <v>21.18678519456106</v>
       </c>
       <c r="U99">
         <v>0.0641</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>3.089577934875742</v>
+        <v>3.058051629417827</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1148013334270031</v>
+        <v>0.1145177432245187</v>
       </c>
       <c r="C100">
-        <v>13.85408595378263</v>
+        <v>13.40920573139268</v>
       </c>
       <c r="D100">
-        <v>64.63138595378263</v>
+        <v>64.79035573139268</v>
       </c>
       <c r="E100">
-        <v>58.4923</v>
+        <v>59.09615</v>
       </c>
       <c r="F100">
-        <v>59.1773</v>
+        <v>59.78115</v>
       </c>
       <c r="G100">
         <v>8.4</v>
@@ -9481,28 +9481,28 @@
         <v>11.6</v>
       </c>
       <c r="M100">
-        <v>3.79326493</v>
+        <v>3.831971715</v>
       </c>
       <c r="N100">
-        <v>7.806735069999999</v>
+        <v>7.768028285</v>
       </c>
       <c r="O100">
-        <v>2.2639531703</v>
+        <v>2.25272820265</v>
       </c>
       <c r="P100">
-        <v>5.5427818997</v>
+        <v>5.51530008235</v>
       </c>
       <c r="Q100">
-        <v>6.142781899699999</v>
+        <v>6.11530008235</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.510027671350152</v>
+        <v>6.946185322451867</v>
       </c>
       <c r="T100">
-        <v>21.18678519456106</v>
+        <v>42.20189763957133</v>
       </c>
       <c r="U100">
         <v>0.0641</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>3.058051629417827</v>
+        <v>3.027162219019667</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1145177432245187</v>
-      </c>
-      <c r="C101">
-        <v>13.40920573139268</v>
-      </c>
-      <c r="D101">
-        <v>64.79035573139268</v>
-      </c>
-      <c r="E101">
-        <v>59.09615</v>
-      </c>
-      <c r="F101">
-        <v>59.78115</v>
-      </c>
-      <c r="G101">
-        <v>8.4</v>
-      </c>
-      <c r="H101">
-        <v>59.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>12.2</v>
-      </c>
-      <c r="K101">
-        <v>0.5999999999999996</v>
-      </c>
-      <c r="L101">
-        <v>11.6</v>
-      </c>
-      <c r="M101">
-        <v>3.831971715</v>
-      </c>
-      <c r="N101">
-        <v>7.768028285</v>
-      </c>
-      <c r="O101">
-        <v>2.25272820265</v>
-      </c>
-      <c r="P101">
-        <v>5.51530008235</v>
-      </c>
-      <c r="Q101">
-        <v>6.11530008235</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.946185322451867</v>
-      </c>
-      <c r="T101">
-        <v>42.20189763957133</v>
-      </c>
-      <c r="U101">
-        <v>0.0641</v>
-      </c>
-      <c r="V101">
-        <v>0.29</v>
-      </c>
-      <c r="W101">
-        <v>0.045511</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ba2/BB</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>3.027162219019667</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
